--- a/Project 4 - Group L - ACD.xlsx
+++ b/Project 4 - Group L - ACD.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="281" documentId="8_{5039B39F-7721-441F-AB60-09115DB97475}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C4B64B2-EFBA-4B8A-9E1C-9ECE06BB6BD2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8655" yWindow="3750" windowWidth="28800" windowHeight="11835" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Project 4" sheetId="6" r:id="rId1"/>
@@ -3407,80 +3407,80 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3794,7 +3794,7 @@
       </c>
     </row>
     <row r="2" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B2" s="68" t="s">
+      <c r="B2" s="61" t="s">
         <v>74</v>
       </c>
       <c r="C2" s="17" t="s">
@@ -3805,7 +3805,7 @@
       </c>
     </row>
     <row r="3" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B3" s="69"/>
+      <c r="B3" s="62"/>
       <c r="C3" s="13" t="s">
         <v>4</v>
       </c>
@@ -3814,7 +3814,7 @@
       </c>
     </row>
     <row r="4" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B4" s="69"/>
+      <c r="B4" s="62"/>
       <c r="C4" s="16" t="s">
         <v>5</v>
       </c>
@@ -3823,7 +3823,7 @@
       </c>
     </row>
     <row r="5" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B5" s="69"/>
+      <c r="B5" s="62"/>
       <c r="C5" s="13" t="s">
         <v>6</v>
       </c>
@@ -3832,7 +3832,7 @@
       </c>
     </row>
     <row r="6" spans="2:4" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="69"/>
+      <c r="B6" s="62"/>
       <c r="C6" s="16" t="s">
         <v>12</v>
       </c>
@@ -3841,7 +3841,7 @@
       </c>
     </row>
     <row r="7" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B7" s="69"/>
+      <c r="B7" s="62"/>
       <c r="C7" s="13" t="s">
         <v>14</v>
       </c>
@@ -3850,7 +3850,7 @@
       </c>
     </row>
     <row r="8" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="69"/>
+      <c r="B8" s="62"/>
       <c r="C8" s="16" t="s">
         <v>16</v>
       </c>
@@ -3859,7 +3859,7 @@
       </c>
     </row>
     <row r="9" spans="2:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="70"/>
+      <c r="B9" s="63"/>
       <c r="C9" s="14" t="s">
         <v>18</v>
       </c>
@@ -3873,7 +3873,7 @@
       <c r="D10" s="9"/>
     </row>
     <row r="11" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B11" s="59" t="s">
+      <c r="B11" s="58" t="s">
         <v>73</v>
       </c>
       <c r="C11" s="20" t="s">
@@ -3884,7 +3884,7 @@
       </c>
     </row>
     <row r="12" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B12" s="60"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="13" t="s">
         <v>22</v>
       </c>
@@ -3893,7 +3893,7 @@
       </c>
     </row>
     <row r="13" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B13" s="60"/>
+      <c r="B13" s="59"/>
       <c r="C13" s="21" t="s">
         <v>24</v>
       </c>
@@ -3902,7 +3902,7 @@
       </c>
     </row>
     <row r="14" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B14" s="60"/>
+      <c r="B14" s="59"/>
       <c r="C14" s="13" t="s">
         <v>26</v>
       </c>
@@ -3911,7 +3911,7 @@
       </c>
     </row>
     <row r="15" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B15" s="60"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="21" t="s">
         <v>28</v>
       </c>
@@ -3920,7 +3920,7 @@
       </c>
     </row>
     <row r="16" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B16" s="60"/>
+      <c r="B16" s="59"/>
       <c r="C16" s="13" t="s">
         <v>30</v>
       </c>
@@ -3929,7 +3929,7 @@
       </c>
     </row>
     <row r="17" spans="2:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="61"/>
+      <c r="B17" s="60"/>
       <c r="C17" s="22" t="s">
         <v>32</v>
       </c>
@@ -3943,7 +3943,7 @@
       <c r="D18" s="9"/>
     </row>
     <row r="19" spans="2:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="64" t="s">
         <v>72</v>
       </c>
       <c r="C19" s="23" t="s">
@@ -3954,7 +3954,7 @@
       </c>
     </row>
     <row r="20" spans="2:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="63"/>
+      <c r="B20" s="65"/>
       <c r="C20" s="13" t="s">
         <v>36</v>
       </c>
@@ -3963,7 +3963,7 @@
       </c>
     </row>
     <row r="21" spans="2:4" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="63"/>
+      <c r="B21" s="65"/>
       <c r="C21" s="25" t="s">
         <v>38</v>
       </c>
@@ -3972,7 +3972,7 @@
       </c>
     </row>
     <row r="22" spans="2:4" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="64"/>
+      <c r="B22" s="66"/>
       <c r="C22" s="14" t="s">
         <v>40</v>
       </c>
@@ -3986,7 +3986,7 @@
       <c r="D23" s="9"/>
     </row>
     <row r="24" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B24" s="65" t="s">
+      <c r="B24" s="67" t="s">
         <v>71</v>
       </c>
       <c r="C24" s="27" t="s">
@@ -3997,7 +3997,7 @@
       </c>
     </row>
     <row r="25" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B25" s="66"/>
+      <c r="B25" s="68"/>
       <c r="C25" s="13" t="s">
         <v>44</v>
       </c>
@@ -4006,7 +4006,7 @@
       </c>
     </row>
     <row r="26" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B26" s="66"/>
+      <c r="B26" s="68"/>
       <c r="C26" s="29" t="s">
         <v>46</v>
       </c>
@@ -4015,7 +4015,7 @@
       </c>
     </row>
     <row r="27" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B27" s="66"/>
+      <c r="B27" s="68"/>
       <c r="C27" s="13" t="s">
         <v>48</v>
       </c>
@@ -4024,7 +4024,7 @@
       </c>
     </row>
     <row r="28" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="66"/>
+      <c r="B28" s="68"/>
       <c r="C28" s="29" t="s">
         <v>50</v>
       </c>
@@ -4033,7 +4033,7 @@
       </c>
     </row>
     <row r="29" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="66"/>
+      <c r="B29" s="68"/>
       <c r="C29" s="13" t="s">
         <v>52</v>
       </c>
@@ -4042,7 +4042,7 @@
       </c>
     </row>
     <row r="30" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="66"/>
+      <c r="B30" s="68"/>
       <c r="C30" s="29" t="s">
         <v>54</v>
       </c>
@@ -4051,7 +4051,7 @@
       </c>
     </row>
     <row r="31" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="66"/>
+      <c r="B31" s="68"/>
       <c r="C31" s="13" t="s">
         <v>56</v>
       </c>
@@ -4060,7 +4060,7 @@
       </c>
     </row>
     <row r="32" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B32" s="66"/>
+      <c r="B32" s="68"/>
       <c r="C32" s="29" t="s">
         <v>58</v>
       </c>
@@ -4069,7 +4069,7 @@
       </c>
     </row>
     <row r="33" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B33" s="66"/>
+      <c r="B33" s="68"/>
       <c r="C33" s="13" t="s">
         <v>60</v>
       </c>
@@ -4078,7 +4078,7 @@
       </c>
     </row>
     <row r="34" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B34" s="66"/>
+      <c r="B34" s="68"/>
       <c r="C34" s="29" t="s">
         <v>62</v>
       </c>
@@ -4087,7 +4087,7 @@
       </c>
     </row>
     <row r="35" spans="2:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="67"/>
+      <c r="B35" s="69"/>
       <c r="C35" s="14" t="s">
         <v>64</v>
       </c>
@@ -4101,7 +4101,7 @@
       <c r="D36" s="9"/>
     </row>
     <row r="37" spans="2:4" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="71" t="s">
+      <c r="B37" s="70" t="s">
         <v>70</v>
       </c>
       <c r="C37" s="31" t="s">
@@ -4126,7 +4126,7 @@
       <c r="D39" s="9"/>
     </row>
     <row r="40" spans="2:4" ht="66.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="68" t="s">
+      <c r="B40" s="61" t="s">
         <v>75</v>
       </c>
       <c r="C40" s="17" t="s">
@@ -4137,7 +4137,7 @@
       </c>
     </row>
     <row r="41" spans="2:4" ht="66.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B41" s="70"/>
+      <c r="B41" s="63"/>
       <c r="C41" s="14" t="s">
         <v>78</v>
       </c>
@@ -4151,7 +4151,7 @@
       <c r="D42" s="9"/>
     </row>
     <row r="43" spans="2:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="59" t="s">
+      <c r="B43" s="58" t="s">
         <v>80</v>
       </c>
       <c r="C43" s="20" t="s">
@@ -4162,7 +4162,7 @@
       </c>
     </row>
     <row r="44" spans="2:4" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="60"/>
+      <c r="B44" s="59"/>
       <c r="C44" s="13" t="s">
         <v>83</v>
       </c>
@@ -4171,7 +4171,7 @@
       </c>
     </row>
     <row r="45" spans="2:4" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B45" s="61"/>
+      <c r="B45" s="60"/>
       <c r="C45" s="22" t="s">
         <v>85</v>
       </c>
@@ -4185,7 +4185,7 @@
       <c r="D46" s="9"/>
     </row>
     <row r="47" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="62" t="s">
+      <c r="B47" s="64" t="s">
         <v>650</v>
       </c>
       <c r="C47" s="23" t="s">
@@ -4196,7 +4196,7 @@
       </c>
     </row>
     <row r="48" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="63"/>
+      <c r="B48" s="65"/>
       <c r="C48" s="13" t="s">
         <v>89</v>
       </c>
@@ -4205,7 +4205,7 @@
       </c>
     </row>
     <row r="49" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="63"/>
+      <c r="B49" s="65"/>
       <c r="C49" s="25" t="s">
         <v>91</v>
       </c>
@@ -4214,7 +4214,7 @@
       </c>
     </row>
     <row r="50" spans="2:4" ht="33" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B50" s="64"/>
+      <c r="B50" s="66"/>
       <c r="C50" s="14" t="s">
         <v>93</v>
       </c>
@@ -4228,7 +4228,7 @@
       <c r="D51" s="9"/>
     </row>
     <row r="52" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B52" s="65" t="s">
+      <c r="B52" s="67" t="s">
         <v>95</v>
       </c>
       <c r="C52" s="27" t="s">
@@ -4239,7 +4239,7 @@
       </c>
     </row>
     <row r="53" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B53" s="66"/>
+      <c r="B53" s="68"/>
       <c r="C53" s="13" t="s">
         <v>98</v>
       </c>
@@ -4248,7 +4248,7 @@
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B54" s="66"/>
+      <c r="B54" s="68"/>
       <c r="C54" s="29" t="s">
         <v>100</v>
       </c>
@@ -4257,7 +4257,7 @@
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B55" s="66"/>
+      <c r="B55" s="68"/>
       <c r="C55" s="13" t="s">
         <v>102</v>
       </c>
@@ -4266,7 +4266,7 @@
       </c>
     </row>
     <row r="56" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B56" s="66"/>
+      <c r="B56" s="68"/>
       <c r="C56" s="29" t="s">
         <v>104</v>
       </c>
@@ -4275,7 +4275,7 @@
       </c>
     </row>
     <row r="57" spans="2:4" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B57" s="66"/>
+      <c r="B57" s="68"/>
       <c r="C57" s="13" t="s">
         <v>106</v>
       </c>
@@ -4284,7 +4284,7 @@
       </c>
     </row>
     <row r="58" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B58" s="66"/>
+      <c r="B58" s="68"/>
       <c r="C58" s="29" t="s">
         <v>108</v>
       </c>
@@ -4293,7 +4293,7 @@
       </c>
     </row>
     <row r="59" spans="2:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B59" s="67"/>
+      <c r="B59" s="69"/>
       <c r="C59" s="14" t="s">
         <v>110</v>
       </c>
@@ -4307,7 +4307,7 @@
       <c r="D60" s="9"/>
     </row>
     <row r="61" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B61" s="71" t="s">
+      <c r="B61" s="70" t="s">
         <v>112</v>
       </c>
       <c r="C61" s="31" t="s">
@@ -4318,7 +4318,7 @@
       </c>
     </row>
     <row r="62" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B62" s="73"/>
+      <c r="B62" s="71"/>
       <c r="C62" s="13" t="s">
         <v>115</v>
       </c>
@@ -4327,7 +4327,7 @@
       </c>
     </row>
     <row r="63" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B63" s="73"/>
+      <c r="B63" s="71"/>
       <c r="C63" s="35" t="s">
         <v>117</v>
       </c>
@@ -4336,7 +4336,7 @@
       </c>
     </row>
     <row r="64" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B64" s="73"/>
+      <c r="B64" s="71"/>
       <c r="C64" s="13" t="s">
         <v>119</v>
       </c>
@@ -4345,7 +4345,7 @@
       </c>
     </row>
     <row r="65" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B65" s="73"/>
+      <c r="B65" s="71"/>
       <c r="C65" s="35" t="s">
         <v>121</v>
       </c>
@@ -4354,7 +4354,7 @@
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B66" s="73"/>
+      <c r="B66" s="71"/>
       <c r="C66" s="13" t="s">
         <v>123</v>
       </c>
@@ -4363,7 +4363,7 @@
       </c>
     </row>
     <row r="67" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B67" s="73"/>
+      <c r="B67" s="71"/>
       <c r="C67" s="35" t="s">
         <v>125</v>
       </c>
@@ -4372,7 +4372,7 @@
       </c>
     </row>
     <row r="68" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B68" s="73"/>
+      <c r="B68" s="71"/>
       <c r="C68" s="13" t="s">
         <v>127</v>
       </c>
@@ -4395,7 +4395,7 @@
       <c r="D70" s="9"/>
     </row>
     <row r="71" spans="2:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="74" t="s">
+      <c r="B71" s="73" t="s">
         <v>131</v>
       </c>
       <c r="C71" s="17" t="s">
@@ -4406,7 +4406,7 @@
       </c>
     </row>
     <row r="72" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B72" s="75"/>
+      <c r="B72" s="74"/>
       <c r="C72" s="13" t="s">
         <v>134</v>
       </c>
@@ -4415,7 +4415,7 @@
       </c>
     </row>
     <row r="73" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B73" s="75"/>
+      <c r="B73" s="74"/>
       <c r="C73" s="16" t="s">
         <v>136</v>
       </c>
@@ -4424,7 +4424,7 @@
       </c>
     </row>
     <row r="74" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B74" s="75"/>
+      <c r="B74" s="74"/>
       <c r="C74" s="13" t="s">
         <v>138</v>
       </c>
@@ -4433,7 +4433,7 @@
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B75" s="75"/>
+      <c r="B75" s="74"/>
       <c r="C75" s="16" t="s">
         <v>140</v>
       </c>
@@ -4442,7 +4442,7 @@
       </c>
     </row>
     <row r="76" spans="2:4" ht="31.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B76" s="76"/>
+      <c r="B76" s="75"/>
       <c r="C76" s="14" t="s">
         <v>142</v>
       </c>
@@ -4456,7 +4456,7 @@
       <c r="D77" s="9"/>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B78" s="59" t="s">
+      <c r="B78" s="58" t="s">
         <v>144</v>
       </c>
       <c r="C78" s="20" t="s">
@@ -4467,7 +4467,7 @@
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B79" s="60"/>
+      <c r="B79" s="59"/>
       <c r="C79" s="13" t="s">
         <v>147</v>
       </c>
@@ -4476,7 +4476,7 @@
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B80" s="60"/>
+      <c r="B80" s="59"/>
       <c r="C80" s="21" t="s">
         <v>149</v>
       </c>
@@ -4485,7 +4485,7 @@
       </c>
     </row>
     <row r="81" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B81" s="60"/>
+      <c r="B81" s="59"/>
       <c r="C81" s="13" t="s">
         <v>142</v>
       </c>
@@ -4494,7 +4494,7 @@
       </c>
     </row>
     <row r="82" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B82" s="60"/>
+      <c r="B82" s="59"/>
       <c r="C82" s="21" t="s">
         <v>152</v>
       </c>
@@ -4503,7 +4503,7 @@
       </c>
     </row>
     <row r="83" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B83" s="60"/>
+      <c r="B83" s="59"/>
       <c r="C83" s="13" t="s">
         <v>154</v>
       </c>
@@ -4512,7 +4512,7 @@
       </c>
     </row>
     <row r="84" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B84" s="60"/>
+      <c r="B84" s="59"/>
       <c r="C84" s="21" t="s">
         <v>156</v>
       </c>
@@ -4521,7 +4521,7 @@
       </c>
     </row>
     <row r="85" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B85" s="60"/>
+      <c r="B85" s="59"/>
       <c r="C85" s="13" t="s">
         <v>158</v>
       </c>
@@ -4530,33 +4530,33 @@
       </c>
     </row>
     <row r="86" spans="2:10" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B86" s="61"/>
+      <c r="B86" s="60"/>
       <c r="C86" s="22" t="s">
         <v>142</v>
       </c>
       <c r="D86" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="E86" s="58"/>
-      <c r="F86" s="58"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="58"/>
-      <c r="I86" s="58"/>
-      <c r="J86" s="58"/>
+      <c r="E86" s="82"/>
+      <c r="F86" s="82"/>
+      <c r="G86" s="82"/>
+      <c r="H86" s="82"/>
+      <c r="I86" s="82"/>
+      <c r="J86" s="82"/>
     </row>
     <row r="87" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B87" s="15"/>
       <c r="C87" s="8"/>
       <c r="D87" s="9"/>
-      <c r="E87" s="58"/>
-      <c r="F87" s="58"/>
-      <c r="G87" s="58"/>
-      <c r="H87" s="58"/>
-      <c r="I87" s="58"/>
-      <c r="J87" s="58"/>
+      <c r="E87" s="82"/>
+      <c r="F87" s="82"/>
+      <c r="G87" s="82"/>
+      <c r="H87" s="82"/>
+      <c r="I87" s="82"/>
+      <c r="J87" s="82"/>
     </row>
     <row r="88" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B88" s="62" t="s">
+      <c r="B88" s="64" t="s">
         <v>177</v>
       </c>
       <c r="C88" s="23" t="s">
@@ -4565,131 +4565,131 @@
       <c r="D88" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="E88" s="58"/>
-      <c r="F88" s="58"/>
-      <c r="G88" s="58"/>
-      <c r="H88" s="58"/>
-      <c r="I88" s="58"/>
-      <c r="J88" s="58"/>
+      <c r="E88" s="82"/>
+      <c r="F88" s="82"/>
+      <c r="G88" s="82"/>
+      <c r="H88" s="82"/>
+      <c r="I88" s="82"/>
+      <c r="J88" s="82"/>
     </row>
     <row r="89" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B89" s="63"/>
+      <c r="B89" s="65"/>
       <c r="C89" s="13" t="s">
         <v>163</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E89" s="58"/>
-      <c r="F89" s="58"/>
-      <c r="G89" s="58"/>
-      <c r="H89" s="58"/>
-      <c r="I89" s="58"/>
-      <c r="J89" s="58"/>
+      <c r="E89" s="82"/>
+      <c r="F89" s="82"/>
+      <c r="G89" s="82"/>
+      <c r="H89" s="82"/>
+      <c r="I89" s="82"/>
+      <c r="J89" s="82"/>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B90" s="63"/>
+      <c r="B90" s="65"/>
       <c r="C90" s="25" t="s">
         <v>165</v>
       </c>
       <c r="D90" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="E90" s="58"/>
-      <c r="F90" s="58"/>
-      <c r="G90" s="58"/>
-      <c r="H90" s="58"/>
-      <c r="I90" s="58"/>
-      <c r="J90" s="58"/>
+      <c r="E90" s="82"/>
+      <c r="F90" s="82"/>
+      <c r="G90" s="82"/>
+      <c r="H90" s="82"/>
+      <c r="I90" s="82"/>
+      <c r="J90" s="82"/>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B91" s="63"/>
+      <c r="B91" s="65"/>
       <c r="C91" s="13" t="s">
         <v>167</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E91" s="58"/>
-      <c r="F91" s="58"/>
-      <c r="G91" s="58"/>
-      <c r="H91" s="58"/>
-      <c r="I91" s="58"/>
-      <c r="J91" s="58"/>
+      <c r="E91" s="82"/>
+      <c r="F91" s="82"/>
+      <c r="G91" s="82"/>
+      <c r="H91" s="82"/>
+      <c r="I91" s="82"/>
+      <c r="J91" s="82"/>
     </row>
     <row r="92" spans="2:10" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B92" s="63"/>
+      <c r="B92" s="65"/>
       <c r="C92" s="25" t="s">
         <v>169</v>
       </c>
       <c r="D92" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="E92" s="58"/>
-      <c r="F92" s="58"/>
-      <c r="G92" s="58"/>
-      <c r="H92" s="58"/>
-      <c r="I92" s="58"/>
-      <c r="J92" s="58"/>
+      <c r="E92" s="82"/>
+      <c r="F92" s="82"/>
+      <c r="G92" s="82"/>
+      <c r="H92" s="82"/>
+      <c r="I92" s="82"/>
+      <c r="J92" s="82"/>
     </row>
     <row r="93" spans="2:10" ht="30.75" x14ac:dyDescent="0.25">
-      <c r="B93" s="63"/>
+      <c r="B93" s="65"/>
       <c r="C93" s="13" t="s">
         <v>171</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E93" s="58"/>
-      <c r="F93" s="58"/>
-      <c r="G93" s="58"/>
-      <c r="H93" s="58"/>
-      <c r="I93" s="58"/>
-      <c r="J93" s="58"/>
+      <c r="E93" s="82"/>
+      <c r="F93" s="82"/>
+      <c r="G93" s="82"/>
+      <c r="H93" s="82"/>
+      <c r="I93" s="82"/>
+      <c r="J93" s="82"/>
     </row>
     <row r="94" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B94" s="63"/>
+      <c r="B94" s="65"/>
       <c r="C94" s="25" t="s">
         <v>173</v>
       </c>
       <c r="D94" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="E94" s="58"/>
-      <c r="F94" s="58"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="58"/>
-      <c r="I94" s="58"/>
-      <c r="J94" s="58"/>
+      <c r="E94" s="82"/>
+      <c r="F94" s="82"/>
+      <c r="G94" s="82"/>
+      <c r="H94" s="82"/>
+      <c r="I94" s="82"/>
+      <c r="J94" s="82"/>
     </row>
     <row r="95" spans="2:10" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B95" s="64"/>
+      <c r="B95" s="66"/>
       <c r="C95" s="14" t="s">
         <v>175</v>
       </c>
       <c r="D95" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E95" s="58"/>
-      <c r="F95" s="58"/>
-      <c r="G95" s="58"/>
-      <c r="H95" s="58"/>
-      <c r="I95" s="58"/>
-      <c r="J95" s="58"/>
+      <c r="E95" s="82"/>
+      <c r="F95" s="82"/>
+      <c r="G95" s="82"/>
+      <c r="H95" s="82"/>
+      <c r="I95" s="82"/>
+      <c r="J95" s="82"/>
     </row>
     <row r="96" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B96" s="15"/>
       <c r="C96" s="8"/>
       <c r="D96" s="9"/>
-      <c r="E96" s="58"/>
-      <c r="F96" s="58"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="58"/>
-      <c r="I96" s="58"/>
-      <c r="J96" s="58"/>
+      <c r="E96" s="82"/>
+      <c r="F96" s="82"/>
+      <c r="G96" s="82"/>
+      <c r="H96" s="82"/>
+      <c r="I96" s="82"/>
+      <c r="J96" s="82"/>
     </row>
     <row r="97" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B97" s="65" t="s">
+      <c r="B97" s="67" t="s">
         <v>178</v>
       </c>
       <c r="C97" s="27" t="s">
@@ -4698,60 +4698,60 @@
       <c r="D97" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="E97" s="58"/>
-      <c r="F97" s="58"/>
-      <c r="G97" s="58"/>
-      <c r="H97" s="58"/>
-      <c r="I97" s="58"/>
-      <c r="J97" s="58"/>
+      <c r="E97" s="82"/>
+      <c r="F97" s="82"/>
+      <c r="G97" s="82"/>
+      <c r="H97" s="82"/>
+      <c r="I97" s="82"/>
+      <c r="J97" s="82"/>
     </row>
     <row r="98" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B98" s="66"/>
+      <c r="B98" s="68"/>
       <c r="C98" s="13" t="s">
         <v>181</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E98" s="58"/>
-      <c r="F98" s="58"/>
-      <c r="G98" s="58"/>
-      <c r="H98" s="58"/>
-      <c r="I98" s="58"/>
-      <c r="J98" s="58"/>
+      <c r="E98" s="82"/>
+      <c r="F98" s="82"/>
+      <c r="G98" s="82"/>
+      <c r="H98" s="82"/>
+      <c r="I98" s="82"/>
+      <c r="J98" s="82"/>
     </row>
     <row r="99" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B99" s="66"/>
+      <c r="B99" s="68"/>
       <c r="C99" s="29" t="s">
         <v>183</v>
       </c>
       <c r="D99" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="E99" s="58"/>
-      <c r="F99" s="58"/>
-      <c r="G99" s="58"/>
-      <c r="H99" s="58"/>
-      <c r="I99" s="58"/>
-      <c r="J99" s="58"/>
+      <c r="E99" s="82"/>
+      <c r="F99" s="82"/>
+      <c r="G99" s="82"/>
+      <c r="H99" s="82"/>
+      <c r="I99" s="82"/>
+      <c r="J99" s="82"/>
     </row>
     <row r="100" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B100" s="66"/>
+      <c r="B100" s="68"/>
       <c r="C100" s="13" t="s">
         <v>185</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E100" s="58"/>
-      <c r="F100" s="58"/>
-      <c r="G100" s="58"/>
-      <c r="H100" s="58"/>
-      <c r="I100" s="58"/>
-      <c r="J100" s="58"/>
+      <c r="E100" s="82"/>
+      <c r="F100" s="82"/>
+      <c r="G100" s="82"/>
+      <c r="H100" s="82"/>
+      <c r="I100" s="82"/>
+      <c r="J100" s="82"/>
     </row>
     <row r="101" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B101" s="66"/>
+      <c r="B101" s="68"/>
       <c r="C101" s="29" t="s">
         <v>187</v>
       </c>
@@ -4760,7 +4760,7 @@
       </c>
     </row>
     <row r="102" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B102" s="66"/>
+      <c r="B102" s="68"/>
       <c r="C102" s="13" t="s">
         <v>189</v>
       </c>
@@ -4769,7 +4769,7 @@
       </c>
     </row>
     <row r="103" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B103" s="66"/>
+      <c r="B103" s="68"/>
       <c r="C103" s="29" t="s">
         <v>191</v>
       </c>
@@ -4778,7 +4778,7 @@
       </c>
     </row>
     <row r="104" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B104" s="66"/>
+      <c r="B104" s="68"/>
       <c r="C104" s="13" t="s">
         <v>193</v>
       </c>
@@ -4787,7 +4787,7 @@
       </c>
     </row>
     <row r="105" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B105" s="67"/>
+      <c r="B105" s="69"/>
       <c r="C105" s="41" t="s">
         <v>195</v>
       </c>
@@ -4801,7 +4801,7 @@
       <c r="D106" s="9"/>
     </row>
     <row r="107" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B107" s="71" t="s">
+      <c r="B107" s="70" t="s">
         <v>197</v>
       </c>
       <c r="C107" s="31" t="s">
@@ -4812,7 +4812,7 @@
       </c>
     </row>
     <row r="108" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B108" s="73"/>
+      <c r="B108" s="71"/>
       <c r="C108" s="13" t="s">
         <v>200</v>
       </c>
@@ -4821,7 +4821,7 @@
       </c>
     </row>
     <row r="109" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B109" s="73"/>
+      <c r="B109" s="71"/>
       <c r="C109" s="35" t="s">
         <v>202</v>
       </c>
@@ -4830,7 +4830,7 @@
       </c>
     </row>
     <row r="110" spans="2:10" ht="30" x14ac:dyDescent="0.25">
-      <c r="B110" s="73"/>
+      <c r="B110" s="71"/>
       <c r="C110" s="13" t="s">
         <v>204</v>
       </c>
@@ -4839,7 +4839,7 @@
       </c>
     </row>
     <row r="111" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B111" s="73"/>
+      <c r="B111" s="71"/>
       <c r="C111" s="35" t="s">
         <v>206</v>
       </c>
@@ -4862,7 +4862,7 @@
       <c r="D113" s="9"/>
     </row>
     <row r="114" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="74" t="s">
+      <c r="B114" s="73" t="s">
         <v>209</v>
       </c>
       <c r="C114" s="43" t="s">
@@ -4873,7 +4873,7 @@
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B115" s="75"/>
+      <c r="B115" s="74"/>
       <c r="C115" s="44" t="s">
         <v>212</v>
       </c>
@@ -4882,7 +4882,7 @@
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B116" s="75"/>
+      <c r="B116" s="74"/>
       <c r="C116" s="45" t="s">
         <v>149</v>
       </c>
@@ -4891,7 +4891,7 @@
       </c>
     </row>
     <row r="117" spans="2:4" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B117" s="75"/>
+      <c r="B117" s="74"/>
       <c r="C117" s="44" t="s">
         <v>142</v>
       </c>
@@ -4900,7 +4900,7 @@
       </c>
     </row>
     <row r="118" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B118" s="75"/>
+      <c r="B118" s="74"/>
       <c r="C118" s="45" t="s">
         <v>216</v>
       </c>
@@ -4909,7 +4909,7 @@
       </c>
     </row>
     <row r="119" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B119" s="75"/>
+      <c r="B119" s="74"/>
       <c r="C119" s="44" t="s">
         <v>218</v>
       </c>
@@ -4918,7 +4918,7 @@
       </c>
     </row>
     <row r="120" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B120" s="75"/>
+      <c r="B120" s="74"/>
       <c r="C120" s="45" t="s">
         <v>156</v>
       </c>
@@ -4927,7 +4927,7 @@
       </c>
     </row>
     <row r="121" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B121" s="75"/>
+      <c r="B121" s="74"/>
       <c r="C121" s="44" t="s">
         <v>158</v>
       </c>
@@ -4936,7 +4936,7 @@
       </c>
     </row>
     <row r="122" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="76"/>
+      <c r="B122" s="75"/>
       <c r="C122" s="46" t="s">
         <v>142</v>
       </c>
@@ -4950,7 +4950,7 @@
       <c r="D123" s="9"/>
     </row>
     <row r="124" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B124" s="59" t="s">
+      <c r="B124" s="58" t="s">
         <v>223</v>
       </c>
       <c r="C124" s="20" t="s">
@@ -4961,7 +4961,7 @@
       </c>
     </row>
     <row r="125" spans="2:4" ht="45" x14ac:dyDescent="0.25">
-      <c r="B125" s="60"/>
+      <c r="B125" s="59"/>
       <c r="C125" s="13" t="s">
         <v>226</v>
       </c>
@@ -4970,7 +4970,7 @@
       </c>
     </row>
     <row r="126" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B126" s="60"/>
+      <c r="B126" s="59"/>
       <c r="C126" s="21" t="s">
         <v>228</v>
       </c>
@@ -4979,7 +4979,7 @@
       </c>
     </row>
     <row r="127" spans="2:4" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="61"/>
+      <c r="B127" s="60"/>
       <c r="C127" s="14" t="s">
         <v>230</v>
       </c>
@@ -4993,7 +4993,7 @@
       <c r="D128" s="9"/>
     </row>
     <row r="129" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B129" s="77" t="s">
+      <c r="B129" s="76" t="s">
         <v>232</v>
       </c>
       <c r="C129" s="47" t="s">
@@ -5004,7 +5004,7 @@
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B130" s="78"/>
+      <c r="B130" s="77"/>
       <c r="C130" s="13" t="s">
         <v>235</v>
       </c>
@@ -5013,7 +5013,7 @@
       </c>
     </row>
     <row r="131" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B131" s="78"/>
+      <c r="B131" s="77"/>
       <c r="C131" s="49" t="s">
         <v>237</v>
       </c>
@@ -5022,7 +5022,7 @@
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B132" s="78"/>
+      <c r="B132" s="77"/>
       <c r="C132" s="13" t="s">
         <v>239</v>
       </c>
@@ -5031,7 +5031,7 @@
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B133" s="78"/>
+      <c r="B133" s="77"/>
       <c r="C133" s="49" t="s">
         <v>241</v>
       </c>
@@ -5040,7 +5040,7 @@
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B134" s="78"/>
+      <c r="B134" s="77"/>
       <c r="C134" s="13" t="s">
         <v>243</v>
       </c>
@@ -5049,7 +5049,7 @@
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B135" s="78"/>
+      <c r="B135" s="77"/>
       <c r="C135" s="49" t="s">
         <v>245</v>
       </c>
@@ -5058,7 +5058,7 @@
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B136" s="78"/>
+      <c r="B136" s="77"/>
       <c r="C136" s="13" t="s">
         <v>247</v>
       </c>
@@ -5067,7 +5067,7 @@
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B137" s="78"/>
+      <c r="B137" s="77"/>
       <c r="C137" s="49" t="s">
         <v>249</v>
       </c>
@@ -5076,7 +5076,7 @@
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B138" s="78"/>
+      <c r="B138" s="77"/>
       <c r="C138" s="13" t="s">
         <v>251</v>
       </c>
@@ -5085,7 +5085,7 @@
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B139" s="78"/>
+      <c r="B139" s="77"/>
       <c r="C139" s="49" t="s">
         <v>253</v>
       </c>
@@ -5094,7 +5094,7 @@
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B140" s="78"/>
+      <c r="B140" s="77"/>
       <c r="C140" s="13" t="s">
         <v>142</v>
       </c>
@@ -5103,7 +5103,7 @@
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B141" s="78"/>
+      <c r="B141" s="77"/>
       <c r="C141" s="49" t="s">
         <v>256</v>
       </c>
@@ -5112,7 +5112,7 @@
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B142" s="78"/>
+      <c r="B142" s="77"/>
       <c r="C142" s="13" t="s">
         <v>258</v>
       </c>
@@ -5121,7 +5121,7 @@
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B143" s="78"/>
+      <c r="B143" s="77"/>
       <c r="C143" s="49" t="s">
         <v>239</v>
       </c>
@@ -5130,7 +5130,7 @@
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B144" s="78"/>
+      <c r="B144" s="77"/>
       <c r="C144" s="13" t="s">
         <v>261</v>
       </c>
@@ -5139,7 +5139,7 @@
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B145" s="78"/>
+      <c r="B145" s="77"/>
       <c r="C145" s="49" t="s">
         <v>243</v>
       </c>
@@ -5148,7 +5148,7 @@
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B146" s="78"/>
+      <c r="B146" s="77"/>
       <c r="C146" s="13" t="s">
         <v>245</v>
       </c>
@@ -5157,7 +5157,7 @@
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B147" s="78"/>
+      <c r="B147" s="77"/>
       <c r="C147" s="49" t="s">
         <v>247</v>
       </c>
@@ -5166,7 +5166,7 @@
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B148" s="78"/>
+      <c r="B148" s="77"/>
       <c r="C148" s="13" t="s">
         <v>249</v>
       </c>
@@ -5175,7 +5175,7 @@
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B149" s="78"/>
+      <c r="B149" s="77"/>
       <c r="C149" s="49" t="s">
         <v>267</v>
       </c>
@@ -5184,7 +5184,7 @@
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B150" s="78"/>
+      <c r="B150" s="77"/>
       <c r="C150" s="13" t="s">
         <v>253</v>
       </c>
@@ -5193,7 +5193,7 @@
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B151" s="78"/>
+      <c r="B151" s="77"/>
       <c r="C151" s="49" t="s">
         <v>142</v>
       </c>
@@ -5202,7 +5202,7 @@
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B152" s="78"/>
+      <c r="B152" s="77"/>
       <c r="C152" s="13" t="s">
         <v>270</v>
       </c>
@@ -5211,7 +5211,7 @@
       </c>
     </row>
     <row r="153" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B153" s="78"/>
+      <c r="B153" s="77"/>
       <c r="C153" s="49" t="s">
         <v>272</v>
       </c>
@@ -5220,7 +5220,7 @@
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B154" s="78"/>
+      <c r="B154" s="77"/>
       <c r="C154" s="13" t="s">
         <v>274</v>
       </c>
@@ -5229,7 +5229,7 @@
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B155" s="78"/>
+      <c r="B155" s="77"/>
       <c r="C155" s="49" t="s">
         <v>276</v>
       </c>
@@ -5238,7 +5238,7 @@
       </c>
     </row>
     <row r="156" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B156" s="79"/>
+      <c r="B156" s="78"/>
       <c r="C156" s="14" t="s">
         <v>7</v>
       </c>
@@ -5252,7 +5252,7 @@
       <c r="D157" s="9"/>
     </row>
     <row r="158" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B158" s="80" t="s">
+      <c r="B158" s="79" t="s">
         <v>279</v>
       </c>
       <c r="C158" s="52" t="s">
@@ -5263,7 +5263,7 @@
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B159" s="81"/>
+      <c r="B159" s="80"/>
       <c r="C159" s="54" t="s">
         <v>281</v>
       </c>
@@ -5272,7 +5272,7 @@
       </c>
     </row>
     <row r="160" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B160" s="81"/>
+      <c r="B160" s="80"/>
       <c r="C160" s="55" t="s">
         <v>283</v>
       </c>
@@ -5281,7 +5281,7 @@
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B161" s="81"/>
+      <c r="B161" s="80"/>
       <c r="C161" s="54" t="s">
         <v>285</v>
       </c>
@@ -5290,7 +5290,7 @@
       </c>
     </row>
     <row r="162" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B162" s="81"/>
+      <c r="B162" s="80"/>
       <c r="C162" s="55" t="s">
         <v>287</v>
       </c>
@@ -5299,7 +5299,7 @@
       </c>
     </row>
     <row r="163" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B163" s="81"/>
+      <c r="B163" s="80"/>
       <c r="C163" s="54" t="s">
         <v>289</v>
       </c>
@@ -5308,7 +5308,7 @@
       </c>
     </row>
     <row r="164" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B164" s="81"/>
+      <c r="B164" s="80"/>
       <c r="C164" s="55" t="s">
         <v>291</v>
       </c>
@@ -5317,7 +5317,7 @@
       </c>
     </row>
     <row r="165" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B165" s="81"/>
+      <c r="B165" s="80"/>
       <c r="C165" s="54" t="s">
         <v>237</v>
       </c>
@@ -5326,7 +5326,7 @@
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B166" s="81"/>
+      <c r="B166" s="80"/>
       <c r="C166" s="55" t="s">
         <v>239</v>
       </c>
@@ -5335,7 +5335,7 @@
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B167" s="81"/>
+      <c r="B167" s="80"/>
       <c r="C167" s="54" t="s">
         <v>295</v>
       </c>
@@ -5344,7 +5344,7 @@
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B168" s="81"/>
+      <c r="B168" s="80"/>
       <c r="C168" s="55" t="s">
         <v>245</v>
       </c>
@@ -5353,7 +5353,7 @@
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B169" s="81"/>
+      <c r="B169" s="80"/>
       <c r="C169" s="54" t="s">
         <v>247</v>
       </c>
@@ -5362,7 +5362,7 @@
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B170" s="81"/>
+      <c r="B170" s="80"/>
       <c r="C170" s="55" t="s">
         <v>299</v>
       </c>
@@ -5371,7 +5371,7 @@
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B171" s="81"/>
+      <c r="B171" s="80"/>
       <c r="C171" s="54" t="s">
         <v>142</v>
       </c>
@@ -5380,7 +5380,7 @@
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B172" s="81"/>
+      <c r="B172" s="80"/>
       <c r="C172" s="55" t="s">
         <v>302</v>
       </c>
@@ -5389,7 +5389,7 @@
       </c>
     </row>
     <row r="173" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B173" s="81"/>
+      <c r="B173" s="80"/>
       <c r="C173" s="54" t="s">
         <v>258</v>
       </c>
@@ -5398,7 +5398,7 @@
       </c>
     </row>
     <row r="174" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B174" s="81"/>
+      <c r="B174" s="80"/>
       <c r="C174" s="55" t="s">
         <v>239</v>
       </c>
@@ -5407,7 +5407,7 @@
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B175" s="81"/>
+      <c r="B175" s="80"/>
       <c r="C175" s="54" t="s">
         <v>306</v>
       </c>
@@ -5416,7 +5416,7 @@
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B176" s="81"/>
+      <c r="B176" s="80"/>
       <c r="C176" s="55" t="s">
         <v>245</v>
       </c>
@@ -5425,7 +5425,7 @@
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B177" s="81"/>
+      <c r="B177" s="80"/>
       <c r="C177" s="54" t="s">
         <v>247</v>
       </c>
@@ -5434,7 +5434,7 @@
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B178" s="81"/>
+      <c r="B178" s="80"/>
       <c r="C178" s="55" t="s">
         <v>310</v>
       </c>
@@ -5443,7 +5443,7 @@
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B179" s="81"/>
+      <c r="B179" s="80"/>
       <c r="C179" s="54" t="s">
         <v>142</v>
       </c>
@@ -5452,7 +5452,7 @@
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B180" s="81"/>
+      <c r="B180" s="80"/>
       <c r="C180" s="55" t="s">
         <v>313</v>
       </c>
@@ -5461,7 +5461,7 @@
       </c>
     </row>
     <row r="181" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B181" s="81"/>
+      <c r="B181" s="80"/>
       <c r="C181" s="54" t="s">
         <v>272</v>
       </c>
@@ -5470,7 +5470,7 @@
       </c>
     </row>
     <row r="182" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B182" s="81"/>
+      <c r="B182" s="80"/>
       <c r="C182" s="55" t="s">
         <v>316</v>
       </c>
@@ -5479,7 +5479,7 @@
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B183" s="81"/>
+      <c r="B183" s="80"/>
       <c r="C183" s="54" t="s">
         <v>318</v>
       </c>
@@ -5488,7 +5488,7 @@
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B184" s="81"/>
+      <c r="B184" s="80"/>
       <c r="C184" s="55" t="s">
         <v>320</v>
       </c>
@@ -5497,7 +5497,7 @@
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B185" s="81"/>
+      <c r="B185" s="80"/>
       <c r="C185" s="54" t="s">
         <v>322</v>
       </c>
@@ -5506,7 +5506,7 @@
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B186" s="81"/>
+      <c r="B186" s="80"/>
       <c r="C186" s="55" t="s">
         <v>324</v>
       </c>
@@ -5515,7 +5515,7 @@
       </c>
     </row>
     <row r="187" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B187" s="81"/>
+      <c r="B187" s="80"/>
       <c r="C187" s="54" t="s">
         <v>276</v>
       </c>
@@ -5524,7 +5524,7 @@
       </c>
     </row>
     <row r="188" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B188" s="82"/>
+      <c r="B188" s="81"/>
       <c r="C188" s="57" t="s">
         <v>7</v>
       </c>
@@ -5538,7 +5538,7 @@
       <c r="D189" s="9"/>
     </row>
     <row r="190" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B190" s="71" t="s">
+      <c r="B190" s="70" t="s">
         <v>328</v>
       </c>
       <c r="C190" s="31" t="s">
@@ -5549,7 +5549,7 @@
       </c>
     </row>
     <row r="191" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B191" s="73"/>
+      <c r="B191" s="71"/>
       <c r="C191" s="13" t="s">
         <v>235</v>
       </c>
@@ -5558,7 +5558,7 @@
       </c>
     </row>
     <row r="192" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B192" s="73"/>
+      <c r="B192" s="71"/>
       <c r="C192" s="35" t="s">
         <v>237</v>
       </c>
@@ -5567,7 +5567,7 @@
       </c>
     </row>
     <row r="193" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B193" s="73"/>
+      <c r="B193" s="71"/>
       <c r="C193" s="13" t="s">
         <v>333</v>
       </c>
@@ -5576,7 +5576,7 @@
       </c>
     </row>
     <row r="194" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B194" s="73"/>
+      <c r="B194" s="71"/>
       <c r="C194" s="35" t="s">
         <v>241</v>
       </c>
@@ -5585,7 +5585,7 @@
       </c>
     </row>
     <row r="195" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B195" s="73"/>
+      <c r="B195" s="71"/>
       <c r="C195" s="13" t="s">
         <v>243</v>
       </c>
@@ -5594,7 +5594,7 @@
       </c>
     </row>
     <row r="196" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B196" s="73"/>
+      <c r="B196" s="71"/>
       <c r="C196" s="35" t="s">
         <v>245</v>
       </c>
@@ -5603,7 +5603,7 @@
       </c>
     </row>
     <row r="197" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B197" s="73"/>
+      <c r="B197" s="71"/>
       <c r="C197" s="13" t="s">
         <v>247</v>
       </c>
@@ -5612,7 +5612,7 @@
       </c>
     </row>
     <row r="198" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B198" s="73"/>
+      <c r="B198" s="71"/>
       <c r="C198" s="35" t="s">
         <v>249</v>
       </c>
@@ -5621,7 +5621,7 @@
       </c>
     </row>
     <row r="199" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B199" s="73"/>
+      <c r="B199" s="71"/>
       <c r="C199" s="13" t="s">
         <v>251</v>
       </c>
@@ -5630,7 +5630,7 @@
       </c>
     </row>
     <row r="200" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B200" s="73"/>
+      <c r="B200" s="71"/>
       <c r="C200" s="35" t="s">
         <v>253</v>
       </c>
@@ -5639,7 +5639,7 @@
       </c>
     </row>
     <row r="201" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="73"/>
+      <c r="B201" s="71"/>
       <c r="C201" s="13" t="s">
         <v>142</v>
       </c>
@@ -5648,7 +5648,7 @@
       </c>
     </row>
     <row r="202" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B202" s="73"/>
+      <c r="B202" s="71"/>
       <c r="C202" s="35" t="s">
         <v>337</v>
       </c>
@@ -5657,7 +5657,7 @@
       </c>
     </row>
     <row r="203" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B203" s="73"/>
+      <c r="B203" s="71"/>
       <c r="C203" s="13" t="s">
         <v>258</v>
       </c>
@@ -5666,7 +5666,7 @@
       </c>
     </row>
     <row r="204" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B204" s="73"/>
+      <c r="B204" s="71"/>
       <c r="C204" s="35" t="s">
         <v>333</v>
       </c>
@@ -5675,7 +5675,7 @@
       </c>
     </row>
     <row r="205" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="73"/>
+      <c r="B205" s="71"/>
       <c r="C205" s="13" t="s">
         <v>261</v>
       </c>
@@ -5684,7 +5684,7 @@
       </c>
     </row>
     <row r="206" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B206" s="73"/>
+      <c r="B206" s="71"/>
       <c r="C206" s="35" t="s">
         <v>243</v>
       </c>
@@ -5693,7 +5693,7 @@
       </c>
     </row>
     <row r="207" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B207" s="73"/>
+      <c r="B207" s="71"/>
       <c r="C207" s="13" t="s">
         <v>245</v>
       </c>
@@ -5702,7 +5702,7 @@
       </c>
     </row>
     <row r="208" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B208" s="73"/>
+      <c r="B208" s="71"/>
       <c r="C208" s="35" t="s">
         <v>247</v>
       </c>
@@ -5711,7 +5711,7 @@
       </c>
     </row>
     <row r="209" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B209" s="73"/>
+      <c r="B209" s="71"/>
       <c r="C209" s="13" t="s">
         <v>249</v>
       </c>
@@ -5720,7 +5720,7 @@
       </c>
     </row>
     <row r="210" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B210" s="73"/>
+      <c r="B210" s="71"/>
       <c r="C210" s="35" t="s">
         <v>267</v>
       </c>
@@ -5729,7 +5729,7 @@
       </c>
     </row>
     <row r="211" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B211" s="73"/>
+      <c r="B211" s="71"/>
       <c r="C211" s="13" t="s">
         <v>253</v>
       </c>
@@ -5738,7 +5738,7 @@
       </c>
     </row>
     <row r="212" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B212" s="73"/>
+      <c r="B212" s="71"/>
       <c r="C212" s="35" t="s">
         <v>142</v>
       </c>
@@ -5747,7 +5747,7 @@
       </c>
     </row>
     <row r="213" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B213" s="73"/>
+      <c r="B213" s="71"/>
       <c r="C213" s="13" t="s">
         <v>343</v>
       </c>
@@ -5756,7 +5756,7 @@
       </c>
     </row>
     <row r="214" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B214" s="73"/>
+      <c r="B214" s="71"/>
       <c r="C214" s="35" t="s">
         <v>272</v>
       </c>
@@ -5765,7 +5765,7 @@
       </c>
     </row>
     <row r="215" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B215" s="73"/>
+      <c r="B215" s="71"/>
       <c r="C215" s="13" t="s">
         <v>346</v>
       </c>
@@ -5774,7 +5774,7 @@
       </c>
     </row>
     <row r="216" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B216" s="73"/>
+      <c r="B216" s="71"/>
       <c r="C216" s="35" t="s">
         <v>276</v>
       </c>
@@ -5796,7 +5796,7 @@
       <c r="D218" s="3"/>
     </row>
     <row r="219" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B219" s="68" t="s">
+      <c r="B219" s="61" t="s">
         <v>350</v>
       </c>
       <c r="C219" s="17" t="s">
@@ -5807,7 +5807,7 @@
       </c>
     </row>
     <row r="220" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B220" s="69"/>
+      <c r="B220" s="62"/>
       <c r="C220" s="13" t="s">
         <v>281</v>
       </c>
@@ -5816,7 +5816,7 @@
       </c>
     </row>
     <row r="221" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B221" s="69"/>
+      <c r="B221" s="62"/>
       <c r="C221" s="16" t="s">
         <v>283</v>
       </c>
@@ -5825,7 +5825,7 @@
       </c>
     </row>
     <row r="222" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B222" s="69"/>
+      <c r="B222" s="62"/>
       <c r="C222" s="13" t="s">
         <v>285</v>
       </c>
@@ -5834,7 +5834,7 @@
       </c>
     </row>
     <row r="223" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B223" s="69"/>
+      <c r="B223" s="62"/>
       <c r="C223" s="16" t="s">
         <v>287</v>
       </c>
@@ -5843,7 +5843,7 @@
       </c>
     </row>
     <row r="224" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B224" s="69"/>
+      <c r="B224" s="62"/>
       <c r="C224" s="13" t="s">
         <v>356</v>
       </c>
@@ -5852,7 +5852,7 @@
       </c>
     </row>
     <row r="225" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B225" s="69"/>
+      <c r="B225" s="62"/>
       <c r="C225" s="16" t="s">
         <v>358</v>
       </c>
@@ -5861,7 +5861,7 @@
       </c>
     </row>
     <row r="226" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B226" s="69"/>
+      <c r="B226" s="62"/>
       <c r="C226" s="13" t="s">
         <v>237</v>
       </c>
@@ -5870,7 +5870,7 @@
       </c>
     </row>
     <row r="227" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B227" s="69"/>
+      <c r="B227" s="62"/>
       <c r="C227" s="16" t="s">
         <v>333</v>
       </c>
@@ -5879,7 +5879,7 @@
       </c>
     </row>
     <row r="228" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B228" s="69"/>
+      <c r="B228" s="62"/>
       <c r="C228" s="13" t="s">
         <v>295</v>
       </c>
@@ -5888,7 +5888,7 @@
       </c>
     </row>
     <row r="229" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B229" s="69"/>
+      <c r="B229" s="62"/>
       <c r="C229" s="16" t="s">
         <v>245</v>
       </c>
@@ -5897,7 +5897,7 @@
       </c>
     </row>
     <row r="230" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B230" s="69"/>
+      <c r="B230" s="62"/>
       <c r="C230" s="13" t="s">
         <v>247</v>
       </c>
@@ -5906,7 +5906,7 @@
       </c>
     </row>
     <row r="231" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B231" s="69"/>
+      <c r="B231" s="62"/>
       <c r="C231" s="16" t="s">
         <v>299</v>
       </c>
@@ -5915,7 +5915,7 @@
       </c>
     </row>
     <row r="232" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B232" s="69"/>
+      <c r="B232" s="62"/>
       <c r="C232" s="13" t="s">
         <v>142</v>
       </c>
@@ -5924,7 +5924,7 @@
       </c>
     </row>
     <row r="233" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B233" s="69"/>
+      <c r="B233" s="62"/>
       <c r="C233" s="16" t="s">
         <v>364</v>
       </c>
@@ -5933,7 +5933,7 @@
       </c>
     </row>
     <row r="234" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B234" s="69"/>
+      <c r="B234" s="62"/>
       <c r="C234" s="13" t="s">
         <v>258</v>
       </c>
@@ -5942,7 +5942,7 @@
       </c>
     </row>
     <row r="235" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B235" s="69"/>
+      <c r="B235" s="62"/>
       <c r="C235" s="16" t="s">
         <v>333</v>
       </c>
@@ -5951,7 +5951,7 @@
       </c>
     </row>
     <row r="236" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B236" s="69"/>
+      <c r="B236" s="62"/>
       <c r="C236" s="13" t="s">
         <v>306</v>
       </c>
@@ -5960,7 +5960,7 @@
       </c>
     </row>
     <row r="237" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B237" s="69"/>
+      <c r="B237" s="62"/>
       <c r="C237" s="16" t="s">
         <v>245</v>
       </c>
@@ -5969,7 +5969,7 @@
       </c>
     </row>
     <row r="238" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B238" s="69"/>
+      <c r="B238" s="62"/>
       <c r="C238" s="13" t="s">
         <v>247</v>
       </c>
@@ -5978,7 +5978,7 @@
       </c>
     </row>
     <row r="239" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B239" s="69"/>
+      <c r="B239" s="62"/>
       <c r="C239" s="16" t="s">
         <v>310</v>
       </c>
@@ -5987,7 +5987,7 @@
       </c>
     </row>
     <row r="240" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B240" s="69"/>
+      <c r="B240" s="62"/>
       <c r="C240" s="13" t="s">
         <v>142</v>
       </c>
@@ -5996,7 +5996,7 @@
       </c>
     </row>
     <row r="241" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B241" s="69"/>
+      <c r="B241" s="62"/>
       <c r="C241" s="16" t="s">
         <v>370</v>
       </c>
@@ -6005,7 +6005,7 @@
       </c>
     </row>
     <row r="242" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B242" s="69"/>
+      <c r="B242" s="62"/>
       <c r="C242" s="13" t="s">
         <v>272</v>
       </c>
@@ -6014,7 +6014,7 @@
       </c>
     </row>
     <row r="243" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B243" s="69"/>
+      <c r="B243" s="62"/>
       <c r="C243" s="16" t="s">
         <v>316</v>
       </c>
@@ -6023,7 +6023,7 @@
       </c>
     </row>
     <row r="244" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B244" s="69"/>
+      <c r="B244" s="62"/>
       <c r="C244" s="13" t="s">
         <v>318</v>
       </c>
@@ -6032,7 +6032,7 @@
       </c>
     </row>
     <row r="245" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B245" s="69"/>
+      <c r="B245" s="62"/>
       <c r="C245" s="16" t="s">
         <v>320</v>
       </c>
@@ -6041,7 +6041,7 @@
       </c>
     </row>
     <row r="246" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B246" s="69"/>
+      <c r="B246" s="62"/>
       <c r="C246" s="13" t="s">
         <v>322</v>
       </c>
@@ -6050,7 +6050,7 @@
       </c>
     </row>
     <row r="247" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B247" s="69"/>
+      <c r="B247" s="62"/>
       <c r="C247" s="16" t="s">
         <v>377</v>
       </c>
@@ -6059,7 +6059,7 @@
       </c>
     </row>
     <row r="248" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B248" s="69"/>
+      <c r="B248" s="62"/>
       <c r="C248" s="13" t="s">
         <v>276</v>
       </c>
@@ -6068,7 +6068,7 @@
       </c>
     </row>
     <row r="249" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B249" s="70"/>
+      <c r="B249" s="63"/>
       <c r="C249" s="33" t="s">
         <v>7</v>
       </c>
@@ -6081,7 +6081,7 @@
       <c r="D250" s="3"/>
     </row>
     <row r="251" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B251" s="59" t="s">
+      <c r="B251" s="58" t="s">
         <v>381</v>
       </c>
       <c r="C251" s="20" t="s">
@@ -6092,7 +6092,7 @@
       </c>
     </row>
     <row r="252" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B252" s="60"/>
+      <c r="B252" s="59"/>
       <c r="C252" s="13" t="s">
         <v>383</v>
       </c>
@@ -6101,7 +6101,7 @@
       </c>
     </row>
     <row r="253" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B253" s="60"/>
+      <c r="B253" s="59"/>
       <c r="C253" s="21" t="s">
         <v>237</v>
       </c>
@@ -6110,7 +6110,7 @@
       </c>
     </row>
     <row r="254" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B254" s="60"/>
+      <c r="B254" s="59"/>
       <c r="C254" s="13" t="s">
         <v>239</v>
       </c>
@@ -6119,7 +6119,7 @@
       </c>
     </row>
     <row r="255" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B255" s="60"/>
+      <c r="B255" s="59"/>
       <c r="C255" s="21" t="s">
         <v>387</v>
       </c>
@@ -6128,7 +6128,7 @@
       </c>
     </row>
     <row r="256" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B256" s="60"/>
+      <c r="B256" s="59"/>
       <c r="C256" s="13" t="s">
         <v>389</v>
       </c>
@@ -6137,7 +6137,7 @@
       </c>
     </row>
     <row r="257" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B257" s="60"/>
+      <c r="B257" s="59"/>
       <c r="C257" s="21" t="s">
         <v>245</v>
       </c>
@@ -6146,7 +6146,7 @@
       </c>
     </row>
     <row r="258" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B258" s="60"/>
+      <c r="B258" s="59"/>
       <c r="C258" s="13" t="s">
         <v>247</v>
       </c>
@@ -6155,7 +6155,7 @@
       </c>
     </row>
     <row r="259" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B259" s="60"/>
+      <c r="B259" s="59"/>
       <c r="C259" s="21" t="s">
         <v>249</v>
       </c>
@@ -6164,7 +6164,7 @@
       </c>
     </row>
     <row r="260" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B260" s="60"/>
+      <c r="B260" s="59"/>
       <c r="C260" s="13" t="s">
         <v>251</v>
       </c>
@@ -6173,7 +6173,7 @@
       </c>
     </row>
     <row r="261" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B261" s="60"/>
+      <c r="B261" s="59"/>
       <c r="C261" s="21" t="s">
         <v>253</v>
       </c>
@@ -6182,7 +6182,7 @@
       </c>
     </row>
     <row r="262" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B262" s="60"/>
+      <c r="B262" s="59"/>
       <c r="C262" s="13" t="s">
         <v>142</v>
       </c>
@@ -6191,7 +6191,7 @@
       </c>
     </row>
     <row r="263" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B263" s="60"/>
+      <c r="B263" s="59"/>
       <c r="C263" s="21" t="s">
         <v>396</v>
       </c>
@@ -6200,7 +6200,7 @@
       </c>
     </row>
     <row r="264" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B264" s="60"/>
+      <c r="B264" s="59"/>
       <c r="C264" s="13" t="s">
         <v>258</v>
       </c>
@@ -6209,7 +6209,7 @@
       </c>
     </row>
     <row r="265" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B265" s="60"/>
+      <c r="B265" s="59"/>
       <c r="C265" s="21" t="s">
         <v>239</v>
       </c>
@@ -6218,7 +6218,7 @@
       </c>
     </row>
     <row r="266" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B266" s="60"/>
+      <c r="B266" s="59"/>
       <c r="C266" s="13" t="s">
         <v>400</v>
       </c>
@@ -6227,7 +6227,7 @@
       </c>
     </row>
     <row r="267" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B267" s="60"/>
+      <c r="B267" s="59"/>
       <c r="C267" s="21" t="s">
         <v>389</v>
       </c>
@@ -6236,7 +6236,7 @@
       </c>
     </row>
     <row r="268" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B268" s="60"/>
+      <c r="B268" s="59"/>
       <c r="C268" s="13" t="s">
         <v>245</v>
       </c>
@@ -6245,7 +6245,7 @@
       </c>
     </row>
     <row r="269" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B269" s="60"/>
+      <c r="B269" s="59"/>
       <c r="C269" s="21" t="s">
         <v>247</v>
       </c>
@@ -6254,7 +6254,7 @@
       </c>
     </row>
     <row r="270" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B270" s="60"/>
+      <c r="B270" s="59"/>
       <c r="C270" s="13" t="s">
         <v>249</v>
       </c>
@@ -6263,7 +6263,7 @@
       </c>
     </row>
     <row r="271" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B271" s="60"/>
+      <c r="B271" s="59"/>
       <c r="C271" s="21" t="s">
         <v>267</v>
       </c>
@@ -6272,7 +6272,7 @@
       </c>
     </row>
     <row r="272" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B272" s="60"/>
+      <c r="B272" s="59"/>
       <c r="C272" s="13" t="s">
         <v>253</v>
       </c>
@@ -6281,7 +6281,7 @@
       </c>
     </row>
     <row r="273" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B273" s="60"/>
+      <c r="B273" s="59"/>
       <c r="C273" s="21" t="s">
         <v>142</v>
       </c>
@@ -6290,7 +6290,7 @@
       </c>
     </row>
     <row r="274" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B274" s="60"/>
+      <c r="B274" s="59"/>
       <c r="C274" s="13" t="s">
         <v>408</v>
       </c>
@@ -6299,7 +6299,7 @@
       </c>
     </row>
     <row r="275" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B275" s="60"/>
+      <c r="B275" s="59"/>
       <c r="C275" s="21" t="s">
         <v>272</v>
       </c>
@@ -6308,7 +6308,7 @@
       </c>
     </row>
     <row r="276" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B276" s="60"/>
+      <c r="B276" s="59"/>
       <c r="C276" s="13" t="s">
         <v>411</v>
       </c>
@@ -6317,7 +6317,7 @@
       </c>
     </row>
     <row r="277" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B277" s="60"/>
+      <c r="B277" s="59"/>
       <c r="C277" s="21" t="s">
         <v>276</v>
       </c>
@@ -6326,7 +6326,7 @@
       </c>
     </row>
     <row r="278" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B278" s="61"/>
+      <c r="B278" s="60"/>
       <c r="C278" s="14" t="s">
         <v>7</v>
       </c>
@@ -6339,7 +6339,7 @@
       <c r="D279" s="3"/>
     </row>
     <row r="280" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B280" s="62" t="s">
+      <c r="B280" s="64" t="s">
         <v>415</v>
       </c>
       <c r="C280" s="23" t="s">
@@ -6350,7 +6350,7 @@
       </c>
     </row>
     <row r="281" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B281" s="63"/>
+      <c r="B281" s="65"/>
       <c r="C281" s="13" t="s">
         <v>417</v>
       </c>
@@ -6359,7 +6359,7 @@
       </c>
     </row>
     <row r="282" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B282" s="63"/>
+      <c r="B282" s="65"/>
       <c r="C282" s="25" t="s">
         <v>283</v>
       </c>
@@ -6368,7 +6368,7 @@
       </c>
     </row>
     <row r="283" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B283" s="63"/>
+      <c r="B283" s="65"/>
       <c r="C283" s="13" t="s">
         <v>420</v>
       </c>
@@ -6377,7 +6377,7 @@
       </c>
     </row>
     <row r="284" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B284" s="63"/>
+      <c r="B284" s="65"/>
       <c r="C284" s="25" t="s">
         <v>422</v>
       </c>
@@ -6386,7 +6386,7 @@
       </c>
     </row>
     <row r="285" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B285" s="63"/>
+      <c r="B285" s="65"/>
       <c r="C285" s="13" t="s">
         <v>424</v>
       </c>
@@ -6395,7 +6395,7 @@
       </c>
     </row>
     <row r="286" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B286" s="63"/>
+      <c r="B286" s="65"/>
       <c r="C286" s="25" t="s">
         <v>426</v>
       </c>
@@ -6404,7 +6404,7 @@
       </c>
     </row>
     <row r="287" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B287" s="63"/>
+      <c r="B287" s="65"/>
       <c r="C287" s="13" t="s">
         <v>237</v>
       </c>
@@ -6413,7 +6413,7 @@
       </c>
     </row>
     <row r="288" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B288" s="63"/>
+      <c r="B288" s="65"/>
       <c r="C288" s="25" t="s">
         <v>239</v>
       </c>
@@ -6422,7 +6422,7 @@
       </c>
     </row>
     <row r="289" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B289" s="63"/>
+      <c r="B289" s="65"/>
       <c r="C289" s="13" t="s">
         <v>295</v>
       </c>
@@ -6431,7 +6431,7 @@
       </c>
     </row>
     <row r="290" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B290" s="63"/>
+      <c r="B290" s="65"/>
       <c r="C290" s="25" t="s">
         <v>245</v>
       </c>
@@ -6440,7 +6440,7 @@
       </c>
     </row>
     <row r="291" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B291" s="63"/>
+      <c r="B291" s="65"/>
       <c r="C291" s="13" t="s">
         <v>247</v>
       </c>
@@ -6449,7 +6449,7 @@
       </c>
     </row>
     <row r="292" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B292" s="63"/>
+      <c r="B292" s="65"/>
       <c r="C292" s="25" t="s">
         <v>299</v>
       </c>
@@ -6458,7 +6458,7 @@
       </c>
     </row>
     <row r="293" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B293" s="63"/>
+      <c r="B293" s="65"/>
       <c r="C293" s="13" t="s">
         <v>142</v>
       </c>
@@ -6467,7 +6467,7 @@
       </c>
     </row>
     <row r="294" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B294" s="63"/>
+      <c r="B294" s="65"/>
       <c r="C294" s="25" t="s">
         <v>435</v>
       </c>
@@ -6476,7 +6476,7 @@
       </c>
     </row>
     <row r="295" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B295" s="63"/>
+      <c r="B295" s="65"/>
       <c r="C295" s="13" t="s">
         <v>258</v>
       </c>
@@ -6485,7 +6485,7 @@
       </c>
     </row>
     <row r="296" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B296" s="63"/>
+      <c r="B296" s="65"/>
       <c r="C296" s="25" t="s">
         <v>239</v>
       </c>
@@ -6494,7 +6494,7 @@
       </c>
     </row>
     <row r="297" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B297" s="63"/>
+      <c r="B297" s="65"/>
       <c r="C297" s="13" t="s">
         <v>306</v>
       </c>
@@ -6503,7 +6503,7 @@
       </c>
     </row>
     <row r="298" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B298" s="63"/>
+      <c r="B298" s="65"/>
       <c r="C298" s="25" t="s">
         <v>245</v>
       </c>
@@ -6512,7 +6512,7 @@
       </c>
     </row>
     <row r="299" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B299" s="63"/>
+      <c r="B299" s="65"/>
       <c r="C299" s="13" t="s">
         <v>247</v>
       </c>
@@ -6521,7 +6521,7 @@
       </c>
     </row>
     <row r="300" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B300" s="63"/>
+      <c r="B300" s="65"/>
       <c r="C300" s="25" t="s">
         <v>310</v>
       </c>
@@ -6530,7 +6530,7 @@
       </c>
     </row>
     <row r="301" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B301" s="63"/>
+      <c r="B301" s="65"/>
       <c r="C301" s="13" t="s">
         <v>142</v>
       </c>
@@ -6539,7 +6539,7 @@
       </c>
     </row>
     <row r="302" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B302" s="63"/>
+      <c r="B302" s="65"/>
       <c r="C302" s="25" t="s">
         <v>444</v>
       </c>
@@ -6548,7 +6548,7 @@
       </c>
     </row>
     <row r="303" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B303" s="63"/>
+      <c r="B303" s="65"/>
       <c r="C303" s="13" t="s">
         <v>272</v>
       </c>
@@ -6557,7 +6557,7 @@
       </c>
     </row>
     <row r="304" spans="2:4" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B304" s="63"/>
+      <c r="B304" s="65"/>
       <c r="C304" s="25" t="s">
         <v>316</v>
       </c>
@@ -6566,7 +6566,7 @@
       </c>
     </row>
     <row r="305" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B305" s="63"/>
+      <c r="B305" s="65"/>
       <c r="C305" s="13" t="s">
         <v>318</v>
       </c>
@@ -6575,7 +6575,7 @@
       </c>
     </row>
     <row r="306" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B306" s="63"/>
+      <c r="B306" s="65"/>
       <c r="C306" s="25" t="s">
         <v>320</v>
       </c>
@@ -6584,7 +6584,7 @@
       </c>
     </row>
     <row r="307" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B307" s="63"/>
+      <c r="B307" s="65"/>
       <c r="C307" s="13" t="s">
         <v>322</v>
       </c>
@@ -6593,7 +6593,7 @@
       </c>
     </row>
     <row r="308" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B308" s="63"/>
+      <c r="B308" s="65"/>
       <c r="C308" s="25" t="s">
         <v>451</v>
       </c>
@@ -6602,7 +6602,7 @@
       </c>
     </row>
     <row r="309" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B309" s="63"/>
+      <c r="B309" s="65"/>
       <c r="C309" s="13" t="s">
         <v>276</v>
       </c>
@@ -6611,7 +6611,7 @@
       </c>
     </row>
     <row r="310" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B310" s="64"/>
+      <c r="B310" s="66"/>
       <c r="C310" s="39" t="s">
         <v>7</v>
       </c>
@@ -6624,7 +6624,7 @@
       <c r="D311" s="3"/>
     </row>
     <row r="312" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B312" s="65" t="s">
+      <c r="B312" s="67" t="s">
         <v>455</v>
       </c>
       <c r="C312" s="27" t="s">
@@ -6635,7 +6635,7 @@
       </c>
     </row>
     <row r="313" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B313" s="66"/>
+      <c r="B313" s="68"/>
       <c r="C313" s="13" t="s">
         <v>383</v>
       </c>
@@ -6644,7 +6644,7 @@
       </c>
     </row>
     <row r="314" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B314" s="66"/>
+      <c r="B314" s="68"/>
       <c r="C314" s="29" t="s">
         <v>237</v>
       </c>
@@ -6653,7 +6653,7 @@
       </c>
     </row>
     <row r="315" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B315" s="66"/>
+      <c r="B315" s="68"/>
       <c r="C315" s="13" t="s">
         <v>333</v>
       </c>
@@ -6662,7 +6662,7 @@
       </c>
     </row>
     <row r="316" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B316" s="66"/>
+      <c r="B316" s="68"/>
       <c r="C316" s="29" t="s">
         <v>387</v>
       </c>
@@ -6671,7 +6671,7 @@
       </c>
     </row>
     <row r="317" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B317" s="66"/>
+      <c r="B317" s="68"/>
       <c r="C317" s="13" t="s">
         <v>389</v>
       </c>
@@ -6680,7 +6680,7 @@
       </c>
     </row>
     <row r="318" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B318" s="66"/>
+      <c r="B318" s="68"/>
       <c r="C318" s="29" t="s">
         <v>245</v>
       </c>
@@ -6689,7 +6689,7 @@
       </c>
     </row>
     <row r="319" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B319" s="66"/>
+      <c r="B319" s="68"/>
       <c r="C319" s="13" t="s">
         <v>247</v>
       </c>
@@ -6698,7 +6698,7 @@
       </c>
     </row>
     <row r="320" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B320" s="66"/>
+      <c r="B320" s="68"/>
       <c r="C320" s="29" t="s">
         <v>249</v>
       </c>
@@ -6707,7 +6707,7 @@
       </c>
     </row>
     <row r="321" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B321" s="66"/>
+      <c r="B321" s="68"/>
       <c r="C321" s="13" t="s">
         <v>251</v>
       </c>
@@ -6716,7 +6716,7 @@
       </c>
     </row>
     <row r="322" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B322" s="66"/>
+      <c r="B322" s="68"/>
       <c r="C322" s="29" t="s">
         <v>253</v>
       </c>
@@ -6725,7 +6725,7 @@
       </c>
     </row>
     <row r="323" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B323" s="66"/>
+      <c r="B323" s="68"/>
       <c r="C323" s="13" t="s">
         <v>142</v>
       </c>
@@ -6734,7 +6734,7 @@
       </c>
     </row>
     <row r="324" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B324" s="66"/>
+      <c r="B324" s="68"/>
       <c r="C324" s="29" t="s">
         <v>461</v>
       </c>
@@ -6743,7 +6743,7 @@
       </c>
     </row>
     <row r="325" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B325" s="66"/>
+      <c r="B325" s="68"/>
       <c r="C325" s="13" t="s">
         <v>258</v>
       </c>
@@ -6752,7 +6752,7 @@
       </c>
     </row>
     <row r="326" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B326" s="66"/>
+      <c r="B326" s="68"/>
       <c r="C326" s="29" t="s">
         <v>333</v>
       </c>
@@ -6761,7 +6761,7 @@
       </c>
     </row>
     <row r="327" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B327" s="66"/>
+      <c r="B327" s="68"/>
       <c r="C327" s="13" t="s">
         <v>400</v>
       </c>
@@ -6770,7 +6770,7 @@
       </c>
     </row>
     <row r="328" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B328" s="66"/>
+      <c r="B328" s="68"/>
       <c r="C328" s="29" t="s">
         <v>389</v>
       </c>
@@ -6779,7 +6779,7 @@
       </c>
     </row>
     <row r="329" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B329" s="66"/>
+      <c r="B329" s="68"/>
       <c r="C329" s="13" t="s">
         <v>245</v>
       </c>
@@ -6788,7 +6788,7 @@
       </c>
     </row>
     <row r="330" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B330" s="66"/>
+      <c r="B330" s="68"/>
       <c r="C330" s="29" t="s">
         <v>247</v>
       </c>
@@ -6797,7 +6797,7 @@
       </c>
     </row>
     <row r="331" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B331" s="66"/>
+      <c r="B331" s="68"/>
       <c r="C331" s="13" t="s">
         <v>249</v>
       </c>
@@ -6806,7 +6806,7 @@
       </c>
     </row>
     <row r="332" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B332" s="66"/>
+      <c r="B332" s="68"/>
       <c r="C332" s="29" t="s">
         <v>267</v>
       </c>
@@ -6815,7 +6815,7 @@
       </c>
     </row>
     <row r="333" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B333" s="66"/>
+      <c r="B333" s="68"/>
       <c r="C333" s="13" t="s">
         <v>253</v>
       </c>
@@ -6824,7 +6824,7 @@
       </c>
     </row>
     <row r="334" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B334" s="66"/>
+      <c r="B334" s="68"/>
       <c r="C334" s="29" t="s">
         <v>142</v>
       </c>
@@ -6833,7 +6833,7 @@
       </c>
     </row>
     <row r="335" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B335" s="66"/>
+      <c r="B335" s="68"/>
       <c r="C335" s="13" t="s">
         <v>467</v>
       </c>
@@ -6842,7 +6842,7 @@
       </c>
     </row>
     <row r="336" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B336" s="66"/>
+      <c r="B336" s="68"/>
       <c r="C336" s="29" t="s">
         <v>272</v>
       </c>
@@ -6851,7 +6851,7 @@
       </c>
     </row>
     <row r="337" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B337" s="66"/>
+      <c r="B337" s="68"/>
       <c r="C337" s="13" t="s">
         <v>470</v>
       </c>
@@ -6860,7 +6860,7 @@
       </c>
     </row>
     <row r="338" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B338" s="66"/>
+      <c r="B338" s="68"/>
       <c r="C338" s="29" t="s">
         <v>276</v>
       </c>
@@ -6869,7 +6869,7 @@
       </c>
     </row>
     <row r="339" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B339" s="67"/>
+      <c r="B339" s="69"/>
       <c r="C339" s="14" t="s">
         <v>7</v>
       </c>
@@ -6882,7 +6882,7 @@
       <c r="D340" s="3"/>
     </row>
     <row r="341" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B341" s="71" t="s">
+      <c r="B341" s="70" t="s">
         <v>474</v>
       </c>
       <c r="C341" s="31" t="s">
@@ -6893,7 +6893,7 @@
       </c>
     </row>
     <row r="342" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B342" s="73"/>
+      <c r="B342" s="71"/>
       <c r="C342" s="13" t="s">
         <v>417</v>
       </c>
@@ -6902,7 +6902,7 @@
       </c>
     </row>
     <row r="343" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B343" s="73"/>
+      <c r="B343" s="71"/>
       <c r="C343" s="35" t="s">
         <v>283</v>
       </c>
@@ -6911,7 +6911,7 @@
       </c>
     </row>
     <row r="344" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B344" s="73"/>
+      <c r="B344" s="71"/>
       <c r="C344" s="13" t="s">
         <v>420</v>
       </c>
@@ -6920,7 +6920,7 @@
       </c>
     </row>
     <row r="345" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B345" s="73"/>
+      <c r="B345" s="71"/>
       <c r="C345" s="35" t="s">
         <v>422</v>
       </c>
@@ -6929,7 +6929,7 @@
       </c>
     </row>
     <row r="346" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B346" s="73"/>
+      <c r="B346" s="71"/>
       <c r="C346" s="13" t="s">
         <v>476</v>
       </c>
@@ -6938,7 +6938,7 @@
       </c>
     </row>
     <row r="347" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B347" s="73"/>
+      <c r="B347" s="71"/>
       <c r="C347" s="35" t="s">
         <v>478</v>
       </c>
@@ -6947,7 +6947,7 @@
       </c>
     </row>
     <row r="348" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B348" s="73"/>
+      <c r="B348" s="71"/>
       <c r="C348" s="13" t="s">
         <v>237</v>
       </c>
@@ -6956,7 +6956,7 @@
       </c>
     </row>
     <row r="349" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B349" s="73"/>
+      <c r="B349" s="71"/>
       <c r="C349" s="35" t="s">
         <v>333</v>
       </c>
@@ -6965,7 +6965,7 @@
       </c>
     </row>
     <row r="350" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B350" s="73"/>
+      <c r="B350" s="71"/>
       <c r="C350" s="13" t="s">
         <v>295</v>
       </c>
@@ -6974,7 +6974,7 @@
       </c>
     </row>
     <row r="351" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B351" s="73"/>
+      <c r="B351" s="71"/>
       <c r="C351" s="35" t="s">
         <v>245</v>
       </c>
@@ -6983,7 +6983,7 @@
       </c>
     </row>
     <row r="352" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B352" s="73"/>
+      <c r="B352" s="71"/>
       <c r="C352" s="13" t="s">
         <v>247</v>
       </c>
@@ -6992,7 +6992,7 @@
       </c>
     </row>
     <row r="353" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B353" s="73"/>
+      <c r="B353" s="71"/>
       <c r="C353" s="35" t="s">
         <v>299</v>
       </c>
@@ -7001,7 +7001,7 @@
       </c>
     </row>
     <row r="354" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B354" s="73"/>
+      <c r="B354" s="71"/>
       <c r="C354" s="13" t="s">
         <v>142</v>
       </c>
@@ -7010,7 +7010,7 @@
       </c>
     </row>
     <row r="355" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B355" s="73"/>
+      <c r="B355" s="71"/>
       <c r="C355" s="35" t="s">
         <v>484</v>
       </c>
@@ -7019,7 +7019,7 @@
       </c>
     </row>
     <row r="356" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B356" s="73"/>
+      <c r="B356" s="71"/>
       <c r="C356" s="13" t="s">
         <v>258</v>
       </c>
@@ -7028,7 +7028,7 @@
       </c>
     </row>
     <row r="357" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B357" s="73"/>
+      <c r="B357" s="71"/>
       <c r="C357" s="35" t="s">
         <v>333</v>
       </c>
@@ -7037,7 +7037,7 @@
       </c>
     </row>
     <row r="358" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B358" s="73"/>
+      <c r="B358" s="71"/>
       <c r="C358" s="13" t="s">
         <v>306</v>
       </c>
@@ -7046,7 +7046,7 @@
       </c>
     </row>
     <row r="359" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B359" s="73"/>
+      <c r="B359" s="71"/>
       <c r="C359" s="35" t="s">
         <v>245</v>
       </c>
@@ -7055,7 +7055,7 @@
       </c>
     </row>
     <row r="360" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B360" s="73"/>
+      <c r="B360" s="71"/>
       <c r="C360" s="13" t="s">
         <v>247</v>
       </c>
@@ -7064,7 +7064,7 @@
       </c>
     </row>
     <row r="361" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B361" s="73"/>
+      <c r="B361" s="71"/>
       <c r="C361" s="35" t="s">
         <v>310</v>
       </c>
@@ -7073,7 +7073,7 @@
       </c>
     </row>
     <row r="362" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B362" s="73"/>
+      <c r="B362" s="71"/>
       <c r="C362" s="13" t="s">
         <v>142</v>
       </c>
@@ -7082,7 +7082,7 @@
       </c>
     </row>
     <row r="363" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B363" s="73"/>
+      <c r="B363" s="71"/>
       <c r="C363" s="35" t="s">
         <v>490</v>
       </c>
@@ -7091,7 +7091,7 @@
       </c>
     </row>
     <row r="364" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B364" s="73"/>
+      <c r="B364" s="71"/>
       <c r="C364" s="13" t="s">
         <v>272</v>
       </c>
@@ -7100,7 +7100,7 @@
       </c>
     </row>
     <row r="365" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B365" s="73"/>
+      <c r="B365" s="71"/>
       <c r="C365" s="35" t="s">
         <v>316</v>
       </c>
@@ -7109,7 +7109,7 @@
       </c>
     </row>
     <row r="366" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B366" s="73"/>
+      <c r="B366" s="71"/>
       <c r="C366" s="13" t="s">
         <v>318</v>
       </c>
@@ -7118,7 +7118,7 @@
       </c>
     </row>
     <row r="367" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B367" s="73"/>
+      <c r="B367" s="71"/>
       <c r="C367" s="35" t="s">
         <v>320</v>
       </c>
@@ -7127,7 +7127,7 @@
       </c>
     </row>
     <row r="368" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B368" s="73"/>
+      <c r="B368" s="71"/>
       <c r="C368" s="13" t="s">
         <v>322</v>
       </c>
@@ -7136,7 +7136,7 @@
       </c>
     </row>
     <row r="369" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B369" s="73"/>
+      <c r="B369" s="71"/>
       <c r="C369" s="35" t="s">
         <v>495</v>
       </c>
@@ -7145,7 +7145,7 @@
       </c>
     </row>
     <row r="370" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B370" s="73"/>
+      <c r="B370" s="71"/>
       <c r="C370" s="13" t="s">
         <v>276</v>
       </c>
@@ -7167,7 +7167,7 @@
       <c r="D372" s="3"/>
     </row>
     <row r="373" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B373" s="68" t="s">
+      <c r="B373" s="61" t="s">
         <v>499</v>
       </c>
       <c r="C373" s="17" t="s">
@@ -7178,7 +7178,7 @@
       </c>
     </row>
     <row r="374" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B374" s="69"/>
+      <c r="B374" s="62"/>
       <c r="C374" s="13" t="s">
         <v>501</v>
       </c>
@@ -7187,7 +7187,7 @@
       </c>
     </row>
     <row r="375" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B375" s="69"/>
+      <c r="B375" s="62"/>
       <c r="C375" s="16" t="s">
         <v>503</v>
       </c>
@@ -7196,7 +7196,7 @@
       </c>
     </row>
     <row r="376" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B376" s="69"/>
+      <c r="B376" s="62"/>
       <c r="C376" s="13" t="s">
         <v>505</v>
       </c>
@@ -7205,7 +7205,7 @@
       </c>
     </row>
     <row r="377" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B377" s="69"/>
+      <c r="B377" s="62"/>
       <c r="C377" s="16" t="s">
         <v>507</v>
       </c>
@@ -7214,7 +7214,7 @@
       </c>
     </row>
     <row r="378" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B378" s="69"/>
+      <c r="B378" s="62"/>
       <c r="C378" s="13" t="s">
         <v>509</v>
       </c>
@@ -7223,7 +7223,7 @@
       </c>
     </row>
     <row r="379" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B379" s="69"/>
+      <c r="B379" s="62"/>
       <c r="C379" s="16" t="s">
         <v>511</v>
       </c>
@@ -7232,7 +7232,7 @@
       </c>
     </row>
     <row r="380" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B380" s="69"/>
+      <c r="B380" s="62"/>
       <c r="C380" s="13" t="s">
         <v>513</v>
       </c>
@@ -7241,7 +7241,7 @@
       </c>
     </row>
     <row r="381" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B381" s="69"/>
+      <c r="B381" s="62"/>
       <c r="C381" s="16" t="s">
         <v>515</v>
       </c>
@@ -7250,7 +7250,7 @@
       </c>
     </row>
     <row r="382" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B382" s="69"/>
+      <c r="B382" s="62"/>
       <c r="C382" s="13" t="s">
         <v>517</v>
       </c>
@@ -7259,7 +7259,7 @@
       </c>
     </row>
     <row r="383" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B383" s="69"/>
+      <c r="B383" s="62"/>
       <c r="C383" s="16" t="s">
         <v>519</v>
       </c>
@@ -7268,7 +7268,7 @@
       </c>
     </row>
     <row r="384" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B384" s="69"/>
+      <c r="B384" s="62"/>
       <c r="C384" s="13" t="s">
         <v>521</v>
       </c>
@@ -7277,7 +7277,7 @@
       </c>
     </row>
     <row r="385" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B385" s="69"/>
+      <c r="B385" s="62"/>
       <c r="C385" s="16" t="s">
         <v>523</v>
       </c>
@@ -7286,7 +7286,7 @@
       </c>
     </row>
     <row r="386" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B386" s="69"/>
+      <c r="B386" s="62"/>
       <c r="C386" s="13" t="s">
         <v>525</v>
       </c>
@@ -7295,7 +7295,7 @@
       </c>
     </row>
     <row r="387" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B387" s="69"/>
+      <c r="B387" s="62"/>
       <c r="C387" s="16" t="s">
         <v>527</v>
       </c>
@@ -7304,7 +7304,7 @@
       </c>
     </row>
     <row r="388" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B388" s="69"/>
+      <c r="B388" s="62"/>
       <c r="C388" s="13" t="s">
         <v>529</v>
       </c>
@@ -7313,7 +7313,7 @@
       </c>
     </row>
     <row r="389" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B389" s="69"/>
+      <c r="B389" s="62"/>
       <c r="C389" s="16" t="s">
         <v>142</v>
       </c>
@@ -7322,7 +7322,7 @@
       </c>
     </row>
     <row r="390" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B390" s="69"/>
+      <c r="B390" s="62"/>
       <c r="C390" s="13" t="s">
         <v>532</v>
       </c>
@@ -7331,7 +7331,7 @@
       </c>
     </row>
     <row r="391" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B391" s="69"/>
+      <c r="B391" s="62"/>
       <c r="C391" s="16" t="s">
         <v>534</v>
       </c>
@@ -7340,7 +7340,7 @@
       </c>
     </row>
     <row r="392" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B392" s="69"/>
+      <c r="B392" s="62"/>
       <c r="C392" s="13" t="s">
         <v>536</v>
       </c>
@@ -7349,7 +7349,7 @@
       </c>
     </row>
     <row r="393" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B393" s="69"/>
+      <c r="B393" s="62"/>
       <c r="C393" s="16" t="s">
         <v>538</v>
       </c>
@@ -7358,7 +7358,7 @@
       </c>
     </row>
     <row r="394" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B394" s="69"/>
+      <c r="B394" s="62"/>
       <c r="C394" s="13" t="s">
         <v>540</v>
       </c>
@@ -7367,7 +7367,7 @@
       </c>
     </row>
     <row r="395" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B395" s="69"/>
+      <c r="B395" s="62"/>
       <c r="C395" s="16" t="s">
         <v>542</v>
       </c>
@@ -7376,7 +7376,7 @@
       </c>
     </row>
     <row r="396" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B396" s="69"/>
+      <c r="B396" s="62"/>
       <c r="C396" s="13" t="s">
         <v>299</v>
       </c>
@@ -7385,7 +7385,7 @@
       </c>
     </row>
     <row r="397" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B397" s="69"/>
+      <c r="B397" s="62"/>
       <c r="C397" s="16" t="s">
         <v>142</v>
       </c>
@@ -7394,7 +7394,7 @@
       </c>
     </row>
     <row r="398" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B398" s="69"/>
+      <c r="B398" s="62"/>
       <c r="C398" s="13" t="s">
         <v>546</v>
       </c>
@@ -7403,7 +7403,7 @@
       </c>
     </row>
     <row r="399" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B399" s="69"/>
+      <c r="B399" s="62"/>
       <c r="C399" s="16" t="s">
         <v>548</v>
       </c>
@@ -7412,7 +7412,7 @@
       </c>
     </row>
     <row r="400" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B400" s="69"/>
+      <c r="B400" s="62"/>
       <c r="C400" s="13" t="s">
         <v>550</v>
       </c>
@@ -7421,7 +7421,7 @@
       </c>
     </row>
     <row r="401" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B401" s="69"/>
+      <c r="B401" s="62"/>
       <c r="C401" s="16" t="s">
         <v>552</v>
       </c>
@@ -7430,7 +7430,7 @@
       </c>
     </row>
     <row r="402" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B402" s="69"/>
+      <c r="B402" s="62"/>
       <c r="C402" s="13" t="s">
         <v>554</v>
       </c>
@@ -7439,7 +7439,7 @@
       </c>
     </row>
     <row r="403" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B403" s="69"/>
+      <c r="B403" s="62"/>
       <c r="C403" s="16" t="s">
         <v>556</v>
       </c>
@@ -7448,7 +7448,7 @@
       </c>
     </row>
     <row r="404" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B404" s="69"/>
+      <c r="B404" s="62"/>
       <c r="C404" s="13" t="s">
         <v>529</v>
       </c>
@@ -7457,7 +7457,7 @@
       </c>
     </row>
     <row r="405" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B405" s="69"/>
+      <c r="B405" s="62"/>
       <c r="C405" s="16" t="s">
         <v>142</v>
       </c>
@@ -7466,7 +7466,7 @@
       </c>
     </row>
     <row r="406" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B406" s="69"/>
+      <c r="B406" s="62"/>
       <c r="C406" s="13" t="s">
         <v>560</v>
       </c>
@@ -7475,7 +7475,7 @@
       </c>
     </row>
     <row r="407" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B407" s="69"/>
+      <c r="B407" s="62"/>
       <c r="C407" s="16" t="s">
         <v>534</v>
       </c>
@@ -7484,7 +7484,7 @@
       </c>
     </row>
     <row r="408" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B408" s="69"/>
+      <c r="B408" s="62"/>
       <c r="C408" s="13" t="s">
         <v>563</v>
       </c>
@@ -7493,7 +7493,7 @@
       </c>
     </row>
     <row r="409" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B409" s="69"/>
+      <c r="B409" s="62"/>
       <c r="C409" s="16" t="s">
         <v>565</v>
       </c>
@@ -7502,7 +7502,7 @@
       </c>
     </row>
     <row r="410" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B410" s="69"/>
+      <c r="B410" s="62"/>
       <c r="C410" s="13" t="s">
         <v>542</v>
       </c>
@@ -7511,7 +7511,7 @@
       </c>
     </row>
     <row r="411" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B411" s="69"/>
+      <c r="B411" s="62"/>
       <c r="C411" s="16" t="s">
         <v>310</v>
       </c>
@@ -7520,7 +7520,7 @@
       </c>
     </row>
     <row r="412" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B412" s="69"/>
+      <c r="B412" s="62"/>
       <c r="C412" s="13" t="s">
         <v>142</v>
       </c>
@@ -7529,7 +7529,7 @@
       </c>
     </row>
     <row r="413" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B413" s="69"/>
+      <c r="B413" s="62"/>
       <c r="C413" s="16" t="s">
         <v>570</v>
       </c>
@@ -7538,7 +7538,7 @@
       </c>
     </row>
     <row r="414" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B414" s="69"/>
+      <c r="B414" s="62"/>
       <c r="C414" s="13" t="s">
         <v>572</v>
       </c>
@@ -7547,7 +7547,7 @@
       </c>
     </row>
     <row r="415" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B415" s="69"/>
+      <c r="B415" s="62"/>
       <c r="C415" s="16" t="s">
         <v>574</v>
       </c>
@@ -7556,7 +7556,7 @@
       </c>
     </row>
     <row r="416" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B416" s="69"/>
+      <c r="B416" s="62"/>
       <c r="C416" s="13" t="s">
         <v>576</v>
       </c>
@@ -7565,7 +7565,7 @@
       </c>
     </row>
     <row r="417" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B417" s="69"/>
+      <c r="B417" s="62"/>
       <c r="C417" s="16" t="s">
         <v>578</v>
       </c>
@@ -7574,7 +7574,7 @@
       </c>
     </row>
     <row r="418" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B418" s="69"/>
+      <c r="B418" s="62"/>
       <c r="C418" s="13" t="s">
         <v>276</v>
       </c>
@@ -7583,7 +7583,7 @@
       </c>
     </row>
     <row r="419" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B419" s="70"/>
+      <c r="B419" s="63"/>
       <c r="C419" s="33" t="s">
         <v>7</v>
       </c>
@@ -7596,7 +7596,7 @@
       <c r="D420" s="3"/>
     </row>
     <row r="421" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B421" s="59" t="s">
+      <c r="B421" s="58" t="s">
         <v>582</v>
       </c>
       <c r="C421" s="20" t="s">
@@ -7607,7 +7607,7 @@
       </c>
     </row>
     <row r="422" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B422" s="60"/>
+      <c r="B422" s="59"/>
       <c r="C422" s="13" t="s">
         <v>501</v>
       </c>
@@ -7616,7 +7616,7 @@
       </c>
     </row>
     <row r="423" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B423" s="60"/>
+      <c r="B423" s="59"/>
       <c r="C423" s="21" t="s">
         <v>503</v>
       </c>
@@ -7625,7 +7625,7 @@
       </c>
     </row>
     <row r="424" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B424" s="60"/>
+      <c r="B424" s="59"/>
       <c r="C424" s="13" t="s">
         <v>586</v>
       </c>
@@ -7634,7 +7634,7 @@
       </c>
     </row>
     <row r="425" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B425" s="60"/>
+      <c r="B425" s="59"/>
       <c r="C425" s="21" t="s">
         <v>588</v>
       </c>
@@ -7643,7 +7643,7 @@
       </c>
     </row>
     <row r="426" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B426" s="60"/>
+      <c r="B426" s="59"/>
       <c r="C426" s="13" t="s">
         <v>590</v>
       </c>
@@ -7652,7 +7652,7 @@
       </c>
     </row>
     <row r="427" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B427" s="60"/>
+      <c r="B427" s="59"/>
       <c r="C427" s="21" t="s">
         <v>592</v>
       </c>
@@ -7661,7 +7661,7 @@
       </c>
     </row>
     <row r="428" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B428" s="60"/>
+      <c r="B428" s="59"/>
       <c r="C428" s="13" t="s">
         <v>594</v>
       </c>
@@ -7670,7 +7670,7 @@
       </c>
     </row>
     <row r="429" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B429" s="60"/>
+      <c r="B429" s="59"/>
       <c r="C429" s="21" t="s">
         <v>596</v>
       </c>
@@ -7679,7 +7679,7 @@
       </c>
     </row>
     <row r="430" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B430" s="60"/>
+      <c r="B430" s="59"/>
       <c r="C430" s="13" t="s">
         <v>598</v>
       </c>
@@ -7688,7 +7688,7 @@
       </c>
     </row>
     <row r="431" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B431" s="60"/>
+      <c r="B431" s="59"/>
       <c r="C431" s="21" t="s">
         <v>600</v>
       </c>
@@ -7697,7 +7697,7 @@
       </c>
     </row>
     <row r="432" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B432" s="60"/>
+      <c r="B432" s="59"/>
       <c r="C432" s="13" t="s">
         <v>602</v>
       </c>
@@ -7706,7 +7706,7 @@
       </c>
     </row>
     <row r="433" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B433" s="60"/>
+      <c r="B433" s="59"/>
       <c r="C433" s="21" t="s">
         <v>604</v>
       </c>
@@ -7715,7 +7715,7 @@
       </c>
     </row>
     <row r="434" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B434" s="60"/>
+      <c r="B434" s="59"/>
       <c r="C434" s="13" t="s">
         <v>525</v>
       </c>
@@ -7724,7 +7724,7 @@
       </c>
     </row>
     <row r="435" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B435" s="60"/>
+      <c r="B435" s="59"/>
       <c r="C435" s="21" t="s">
         <v>606</v>
       </c>
@@ -7733,7 +7733,7 @@
       </c>
     </row>
     <row r="436" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B436" s="60"/>
+      <c r="B436" s="59"/>
       <c r="C436" s="13" t="s">
         <v>529</v>
       </c>
@@ -7742,7 +7742,7 @@
       </c>
     </row>
     <row r="437" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B437" s="60"/>
+      <c r="B437" s="59"/>
       <c r="C437" s="21" t="s">
         <v>142</v>
       </c>
@@ -7751,7 +7751,7 @@
       </c>
     </row>
     <row r="438" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B438" s="60"/>
+      <c r="B438" s="59"/>
       <c r="C438" s="13" t="s">
         <v>610</v>
       </c>
@@ -7760,7 +7760,7 @@
       </c>
     </row>
     <row r="439" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B439" s="60"/>
+      <c r="B439" s="59"/>
       <c r="C439" s="21" t="s">
         <v>534</v>
       </c>
@@ -7769,7 +7769,7 @@
       </c>
     </row>
     <row r="440" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B440" s="60"/>
+      <c r="B440" s="59"/>
       <c r="C440" s="13" t="s">
         <v>613</v>
       </c>
@@ -7778,7 +7778,7 @@
       </c>
     </row>
     <row r="441" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B441" s="60"/>
+      <c r="B441" s="59"/>
       <c r="C441" s="21" t="s">
         <v>538</v>
       </c>
@@ -7787,7 +7787,7 @@
       </c>
     </row>
     <row r="442" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B442" s="60"/>
+      <c r="B442" s="59"/>
       <c r="C442" s="13" t="s">
         <v>540</v>
       </c>
@@ -7796,7 +7796,7 @@
       </c>
     </row>
     <row r="443" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B443" s="60"/>
+      <c r="B443" s="59"/>
       <c r="C443" s="21" t="s">
         <v>542</v>
       </c>
@@ -7805,7 +7805,7 @@
       </c>
     </row>
     <row r="444" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B444" s="60"/>
+      <c r="B444" s="59"/>
       <c r="C444" s="13" t="s">
         <v>299</v>
       </c>
@@ -7814,7 +7814,7 @@
       </c>
     </row>
     <row r="445" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B445" s="60"/>
+      <c r="B445" s="59"/>
       <c r="C445" s="21" t="s">
         <v>142</v>
       </c>
@@ -7823,7 +7823,7 @@
       </c>
     </row>
     <row r="446" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B446" s="60"/>
+      <c r="B446" s="59"/>
       <c r="C446" s="13" t="s">
         <v>620</v>
       </c>
@@ -7832,7 +7832,7 @@
       </c>
     </row>
     <row r="447" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B447" s="60"/>
+      <c r="B447" s="59"/>
       <c r="C447" s="21" t="s">
         <v>548</v>
       </c>
@@ -7841,7 +7841,7 @@
       </c>
     </row>
     <row r="448" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B448" s="60"/>
+      <c r="B448" s="59"/>
       <c r="C448" s="13" t="s">
         <v>550</v>
       </c>
@@ -7850,7 +7850,7 @@
       </c>
     </row>
     <row r="449" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B449" s="60"/>
+      <c r="B449" s="59"/>
       <c r="C449" s="21" t="s">
         <v>624</v>
       </c>
@@ -7859,7 +7859,7 @@
       </c>
     </row>
     <row r="450" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B450" s="60"/>
+      <c r="B450" s="59"/>
       <c r="C450" s="13" t="s">
         <v>554</v>
       </c>
@@ -7868,7 +7868,7 @@
       </c>
     </row>
     <row r="451" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B451" s="60"/>
+      <c r="B451" s="59"/>
       <c r="C451" s="21" t="s">
         <v>627</v>
       </c>
@@ -7877,7 +7877,7 @@
       </c>
     </row>
     <row r="452" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B452" s="60"/>
+      <c r="B452" s="59"/>
       <c r="C452" s="13" t="s">
         <v>529</v>
       </c>
@@ -7886,7 +7886,7 @@
       </c>
     </row>
     <row r="453" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B453" s="60"/>
+      <c r="B453" s="59"/>
       <c r="C453" s="21" t="s">
         <v>142</v>
       </c>
@@ -7895,7 +7895,7 @@
       </c>
     </row>
     <row r="454" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B454" s="60"/>
+      <c r="B454" s="59"/>
       <c r="C454" s="13" t="s">
         <v>631</v>
       </c>
@@ -7904,7 +7904,7 @@
       </c>
     </row>
     <row r="455" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B455" s="60"/>
+      <c r="B455" s="59"/>
       <c r="C455" s="21" t="s">
         <v>534</v>
       </c>
@@ -7913,7 +7913,7 @@
       </c>
     </row>
     <row r="456" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B456" s="60"/>
+      <c r="B456" s="59"/>
       <c r="C456" s="13" t="s">
         <v>634</v>
       </c>
@@ -7922,7 +7922,7 @@
       </c>
     </row>
     <row r="457" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B457" s="60"/>
+      <c r="B457" s="59"/>
       <c r="C457" s="21" t="s">
         <v>538</v>
       </c>
@@ -7931,7 +7931,7 @@
       </c>
     </row>
     <row r="458" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B458" s="60"/>
+      <c r="B458" s="59"/>
       <c r="C458" s="13" t="s">
         <v>540</v>
       </c>
@@ -7940,7 +7940,7 @@
       </c>
     </row>
     <row r="459" spans="2:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="B459" s="60"/>
+      <c r="B459" s="59"/>
       <c r="C459" s="21" t="s">
         <v>542</v>
       </c>
@@ -7949,7 +7949,7 @@
       </c>
     </row>
     <row r="460" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B460" s="60"/>
+      <c r="B460" s="59"/>
       <c r="C460" s="13" t="s">
         <v>310</v>
       </c>
@@ -7958,7 +7958,7 @@
       </c>
     </row>
     <row r="461" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B461" s="60"/>
+      <c r="B461" s="59"/>
       <c r="C461" s="21" t="s">
         <v>142</v>
       </c>
@@ -7967,7 +7967,7 @@
       </c>
     </row>
     <row r="462" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B462" s="60"/>
+      <c r="B462" s="59"/>
       <c r="C462" s="13" t="s">
         <v>641</v>
       </c>
@@ -7976,7 +7976,7 @@
       </c>
     </row>
     <row r="463" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B463" s="60"/>
+      <c r="B463" s="59"/>
       <c r="C463" s="21" t="s">
         <v>572</v>
       </c>
@@ -7985,7 +7985,7 @@
       </c>
     </row>
     <row r="464" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B464" s="60"/>
+      <c r="B464" s="59"/>
       <c r="C464" s="13" t="s">
         <v>574</v>
       </c>
@@ -7994,7 +7994,7 @@
       </c>
     </row>
     <row r="465" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B465" s="60"/>
+      <c r="B465" s="59"/>
       <c r="C465" s="21" t="s">
         <v>645</v>
       </c>
@@ -8003,7 +8003,7 @@
       </c>
     </row>
     <row r="466" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B466" s="60"/>
+      <c r="B466" s="59"/>
       <c r="C466" s="13" t="s">
         <v>578</v>
       </c>
@@ -8012,7 +8012,7 @@
       </c>
     </row>
     <row r="467" spans="2:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B467" s="60"/>
+      <c r="B467" s="59"/>
       <c r="C467" s="21" t="s">
         <v>276</v>
       </c>
@@ -8021,7 +8021,7 @@
       </c>
     </row>
     <row r="468" spans="2:4" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B468" s="61"/>
+      <c r="B468" s="60"/>
       <c r="C468" s="14" t="s">
         <v>7</v>
       </c>
@@ -8031,13 +8031,15 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B421:B468"/>
-    <mergeCell ref="B219:B249"/>
-    <mergeCell ref="B251:B278"/>
-    <mergeCell ref="B280:B310"/>
-    <mergeCell ref="B312:B339"/>
-    <mergeCell ref="B341:B371"/>
-    <mergeCell ref="B373:B419"/>
+    <mergeCell ref="E86:J100"/>
+    <mergeCell ref="B78:B86"/>
+    <mergeCell ref="B88:B95"/>
+    <mergeCell ref="B97:B105"/>
+    <mergeCell ref="B2:B9"/>
+    <mergeCell ref="B11:B17"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="B24:B35"/>
+    <mergeCell ref="B37:B38"/>
     <mergeCell ref="B190:B217"/>
     <mergeCell ref="B40:B41"/>
     <mergeCell ref="B43:B45"/>
@@ -8050,15 +8052,13 @@
     <mergeCell ref="B124:B127"/>
     <mergeCell ref="B129:B156"/>
     <mergeCell ref="B158:B188"/>
-    <mergeCell ref="E86:J100"/>
-    <mergeCell ref="B78:B86"/>
-    <mergeCell ref="B88:B95"/>
-    <mergeCell ref="B97:B105"/>
-    <mergeCell ref="B2:B9"/>
-    <mergeCell ref="B11:B17"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="B24:B35"/>
-    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B421:B468"/>
+    <mergeCell ref="B219:B249"/>
+    <mergeCell ref="B251:B278"/>
+    <mergeCell ref="B280:B310"/>
+    <mergeCell ref="B312:B339"/>
+    <mergeCell ref="B341:B371"/>
+    <mergeCell ref="B373:B419"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
